--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\modelX\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\data\prod_parameters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="74">
   <si>
     <t>value</t>
   </si>
@@ -223,6 +223,24 @@
   </si>
   <si>
     <t>of total N, Assume same as bulls</t>
+  </si>
+  <si>
+    <t>poultry</t>
+  </si>
+  <si>
+    <t>broiler</t>
+  </si>
+  <si>
+    <t>broilers</t>
+  </si>
+  <si>
+    <t>Assume same as laying hens for the parent animals</t>
+  </si>
+  <si>
+    <t>Assume same as laying hens for parent animals</t>
+  </si>
+  <si>
+    <t>of total N, assume same as laying hens for parent animals</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -2086,227 +2104,201 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="A42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
       <c r="E43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>70</v>
+      </c>
+      <c r="E44" t="s">
         <v>25</v>
       </c>
-      <c r="G43" t="s">
-        <v>32</v>
-      </c>
-      <c r="H43" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43">
-        <v>0.01</v>
-      </c>
-      <c r="J43" t="s">
-        <v>22</v>
-      </c>
-      <c r="K43" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E44" t="s">
+      <c r="H44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45">
+        <v>9</v>
+      </c>
+      <c r="J45" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" t="s">
         <v>26</v>
       </c>
-      <c r="G44" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44" t="s">
-        <v>22</v>
-      </c>
-      <c r="K44" t="s">
-        <v>59</v>
-      </c>
-      <c r="L44" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E45" t="s">
-        <v>27</v>
-      </c>
-      <c r="G45" t="s">
-        <v>32</v>
-      </c>
-      <c r="H45" t="s">
-        <v>31</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" t="s">
-        <v>59</v>
-      </c>
-      <c r="L45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E46" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46" t="s">
-        <v>33</v>
-      </c>
       <c r="H46" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I46">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
       </c>
-      <c r="K46" t="s">
-        <v>30</v>
-      </c>
-      <c r="L46" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
+        <v>69</v>
+      </c>
       <c r="E47" t="s">
         <v>26</v>
       </c>
-      <c r="G47" t="s">
-        <v>33</v>
-      </c>
       <c r="H47" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I47">
-        <v>0.5</v>
+        <v>86</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
       </c>
       <c r="K47" t="s">
-        <v>30</v>
-      </c>
-      <c r="L47" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
+        <v>70</v>
+      </c>
       <c r="E48" t="s">
         <v>27</v>
       </c>
-      <c r="G48" t="s">
-        <v>33</v>
-      </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
       </c>
-      <c r="K48" t="s">
-        <v>30</v>
-      </c>
-      <c r="L48" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" t="s">
+        <v>69</v>
+      </c>
       <c r="E49" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I49">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
       </c>
       <c r="K49" t="s">
-        <v>59</v>
-      </c>
-      <c r="L49" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E50" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" t="s">
-        <v>34</v>
-      </c>
-      <c r="H50" t="s">
-        <v>31</v>
-      </c>
-      <c r="I50">
-        <v>30</v>
-      </c>
-      <c r="J50" t="s">
-        <v>22</v>
-      </c>
-      <c r="K50" t="s">
-        <v>59</v>
-      </c>
-      <c r="L50" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E51" t="s">
-        <v>27</v>
-      </c>
-      <c r="G51" t="s">
-        <v>34</v>
-      </c>
-      <c r="H51" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51">
-        <v>30</v>
-      </c>
-      <c r="J51" t="s">
-        <v>22</v>
-      </c>
-      <c r="K51" t="s">
-        <v>59</v>
-      </c>
-      <c r="L51" t="s">
-        <v>23</v>
-      </c>
+      <c r="A51" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -2453,251 +2445,203 @@
       <c r="K58" t="s">
         <v>19</v>
       </c>
+      <c r="L58" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D59" t="s">
+        <v>52</v>
       </c>
       <c r="H59" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>22.5</v>
       </c>
       <c r="J59" t="s">
-        <v>22</v>
-      </c>
-      <c r="K59" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D60" t="s">
+        <v>53</v>
       </c>
       <c r="H60" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J60" t="s">
-        <v>22</v>
-      </c>
-      <c r="K60" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>27</v>
-      </c>
-      <c r="G61" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D61" t="s">
+        <v>54</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I61">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="s">
-        <v>22</v>
-      </c>
-      <c r="K61" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D62" t="s">
+        <v>55</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J62" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K62" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E63" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H63" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I63">
-        <v>18</v>
+        <v>9.5</v>
       </c>
       <c r="J63" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K63" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>3</v>
-      </c>
-      <c r="E64" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I64">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J64" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K64" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I65">
-        <v>18</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J65" t="s">
-        <v>22</v>
-      </c>
-      <c r="K65" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" t="s">
-        <v>28</v>
+        <v>68</v>
+      </c>
+      <c r="C66" t="s">
+        <v>69</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I66">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K66" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1</v>
       </c>
-      <c r="D67" t="s">
-        <v>16</v>
-      </c>
       <c r="E67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G67" t="s">
         <v>28</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I67">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J67" t="s">
         <v>22</v>
@@ -2713,9 +2657,6 @@
       <c r="A68" t="s">
         <v>1</v>
       </c>
-      <c r="D68" t="s">
-        <v>17</v>
-      </c>
       <c r="E68" t="s">
         <v>26</v>
       </c>
@@ -2723,10 +2664,10 @@
         <v>28</v>
       </c>
       <c r="H68" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I68">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
@@ -2742,43 +2683,43 @@
       <c r="A69" t="s">
         <v>1</v>
       </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
       <c r="E69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G69" t="s">
         <v>28</v>
       </c>
       <c r="H69" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I69">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J69" t="s">
         <v>22</v>
       </c>
       <c r="K69" t="s">
-        <v>67</v>
+        <v>30</v>
+      </c>
+      <c r="L69" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E70" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G70" t="s">
         <v>28</v>
       </c>
       <c r="H70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I70">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J70" t="s">
         <v>22</v>
@@ -2792,16 +2733,19 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G71" t="s">
+        <v>28</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I71">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
@@ -2815,22 +2759,19 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E72" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="G72" t="s">
+        <v>28</v>
       </c>
       <c r="H72" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I72">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -2844,22 +2785,25 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D73" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="E73" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="G73" t="s">
+        <v>28</v>
       </c>
       <c r="H73" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I73">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -2873,25 +2817,28 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" t="s">
-        <v>13</v>
+        <v>68</v>
+      </c>
+      <c r="C74" t="s">
+        <v>69</v>
       </c>
       <c r="E74" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="G74" t="s">
+        <v>28</v>
       </c>
       <c r="H74" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I74">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
       </c>
       <c r="K74" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L74" t="s">
         <v>23</v>
@@ -2899,25 +2846,28 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C75" t="s">
+        <v>69</v>
       </c>
       <c r="E75" t="s">
         <v>26</v>
       </c>
+      <c r="G75" t="s">
+        <v>28</v>
+      </c>
       <c r="H75" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I75">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="J75" t="s">
         <v>22</v>
       </c>
       <c r="K75" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L75" t="s">
         <v>23</v>
@@ -2925,25 +2875,28 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" t="s">
-        <v>16</v>
+        <v>68</v>
+      </c>
+      <c r="C76" t="s">
+        <v>69</v>
       </c>
       <c r="E76" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="G76" t="s">
+        <v>28</v>
       </c>
       <c r="H76" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76">
         <v>35</v>
       </c>
-      <c r="I76">
-        <v>52</v>
-      </c>
       <c r="J76" t="s">
         <v>22</v>
       </c>
       <c r="K76" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L76" t="s">
         <v>23</v>
@@ -2953,17 +2906,17 @@
       <c r="A77" t="s">
         <v>1</v>
       </c>
-      <c r="D77" t="s">
-        <v>17</v>
-      </c>
       <c r="E77" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="G77" t="s">
+        <v>28</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I77">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -2979,37 +2932,55 @@
       <c r="A78" t="s">
         <v>1</v>
       </c>
+      <c r="C78" t="s">
+        <v>2</v>
+      </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E78" t="s">
         <v>26</v>
       </c>
+      <c r="G78" t="s">
+        <v>28</v>
+      </c>
       <c r="H78" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I78">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
       </c>
       <c r="K78" t="s">
-        <v>67</v>
+        <v>30</v>
+      </c>
+      <c r="L78" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1</v>
       </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" t="s">
+        <v>3</v>
+      </c>
       <c r="E79" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="G79" t="s">
+        <v>28</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I79">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
@@ -3023,134 +2994,173 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>52</v>
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" t="s">
+        <v>28</v>
       </c>
       <c r="H80" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I80">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="J80" t="s">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="K80" t="s">
+        <v>30</v>
       </c>
       <c r="L80" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>53</v>
+        <v>14</v>
+      </c>
+      <c r="E81" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" t="s">
+        <v>28</v>
       </c>
       <c r="H81" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I81">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J81" t="s">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="K81" t="s">
+        <v>30</v>
       </c>
       <c r="L81" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>54</v>
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" t="s">
+        <v>28</v>
       </c>
       <c r="H82" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I82">
-        <v>1.2</v>
+        <v>17</v>
       </c>
       <c r="J82" t="s">
-        <v>8</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>58</v>
+        <v>22</v>
+      </c>
+      <c r="K82" t="s">
+        <v>30</v>
       </c>
       <c r="L82" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>55</v>
+        <v>17</v>
+      </c>
+      <c r="E83" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" t="s">
+        <v>28</v>
       </c>
       <c r="H83" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I83">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J83" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K83" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="L83" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>46</v>
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" t="s">
+        <v>28</v>
       </c>
       <c r="H84" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I84">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J84" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K84" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="L84" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>45</v>
-      </c>
-      <c r="D85" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>27</v>
+      </c>
+      <c r="G85" t="s">
+        <v>28</v>
       </c>
       <c r="H85" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I85">
-        <v>9.5</v>
+        <v>30</v>
       </c>
       <c r="J85" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K85" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="L85" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,10 +3174,10 @@
         <v>28</v>
       </c>
       <c r="H86" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I86">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J86" t="s">
         <v>22</v>
@@ -3190,10 +3200,10 @@
         <v>28</v>
       </c>
       <c r="H87" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I87">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
@@ -3216,10 +3226,10 @@
         <v>28</v>
       </c>
       <c r="H88" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I88">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J88" t="s">
         <v>22</v>
@@ -3233,10 +3243,16 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>45</v>
+        <v>68</v>
+      </c>
+      <c r="C89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" t="s">
+        <v>70</v>
       </c>
       <c r="E89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G89" t="s">
         <v>28</v>
@@ -3245,7 +3261,7 @@
         <v>31</v>
       </c>
       <c r="I89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J89" t="s">
         <v>22</v>
@@ -3259,10 +3275,16 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>45</v>
+        <v>68</v>
+      </c>
+      <c r="C90" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" t="s">
+        <v>70</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G90" t="s">
         <v>28</v>
@@ -3271,7 +3293,7 @@
         <v>31</v>
       </c>
       <c r="I90">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J90" t="s">
         <v>22</v>
@@ -3285,10 +3307,13 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>68</v>
+      </c>
+      <c r="C91" t="s">
+        <v>69</v>
       </c>
       <c r="E91" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G91" t="s">
         <v>28</v>
@@ -3297,13 +3322,13 @@
         <v>31</v>
       </c>
       <c r="I91">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J91" t="s">
         <v>22</v>
       </c>
       <c r="K91" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L91" t="s">
         <v>23</v>
@@ -3311,232 +3336,348 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>68</v>
+      </c>
+      <c r="C92" t="s">
+        <v>69</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G92" t="s">
+        <v>28</v>
       </c>
       <c r="H92" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I92">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="J92" t="s">
         <v>22</v>
       </c>
       <c r="K92" t="s">
-        <v>30</v>
+        <v>73</v>
+      </c>
+      <c r="L92" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>45</v>
+        <v>68</v>
+      </c>
+      <c r="C93" t="s">
+        <v>69</v>
       </c>
       <c r="E93" t="s">
+        <v>27</v>
+      </c>
+      <c r="G93" t="s">
+        <v>28</v>
+      </c>
+      <c r="H93" t="s">
+        <v>31</v>
+      </c>
+      <c r="I93">
+        <v>20</v>
+      </c>
+      <c r="J93" t="s">
+        <v>22</v>
+      </c>
+      <c r="K93" t="s">
+        <v>73</v>
+      </c>
+      <c r="L93" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E94" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" t="s">
+        <v>32</v>
+      </c>
+      <c r="H94" t="s">
+        <v>31</v>
+      </c>
+      <c r="I94">
+        <v>0.01</v>
+      </c>
+      <c r="J94" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" t="s">
+        <v>59</v>
+      </c>
+      <c r="L94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E95" t="s">
         <v>26</v>
       </c>
-      <c r="H93" t="s">
-        <v>35</v>
-      </c>
-      <c r="I93">
-        <v>51</v>
-      </c>
-      <c r="J93" t="s">
-        <v>22</v>
-      </c>
-      <c r="K93" t="s">
+      <c r="G95" t="s">
+        <v>32</v>
+      </c>
+      <c r="H95" t="s">
+        <v>31</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" t="s">
+        <v>59</v>
+      </c>
+      <c r="L95" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E96" t="s">
+        <v>27</v>
+      </c>
+      <c r="G96" t="s">
+        <v>32</v>
+      </c>
+      <c r="H96" t="s">
+        <v>31</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" t="s">
+        <v>59</v>
+      </c>
+      <c r="L96" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E97" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" t="s">
+        <v>33</v>
+      </c>
+      <c r="H97" t="s">
+        <v>31</v>
+      </c>
+      <c r="I97">
+        <v>0.5</v>
+      </c>
+      <c r="J97" t="s">
+        <v>22</v>
+      </c>
+      <c r="K97" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>45</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="L97" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E98" t="s">
+        <v>26</v>
+      </c>
+      <c r="G98" t="s">
+        <v>33</v>
+      </c>
+      <c r="H98" t="s">
+        <v>31</v>
+      </c>
+      <c r="I98">
+        <v>0.5</v>
+      </c>
+      <c r="J98" t="s">
+        <v>22</v>
+      </c>
+      <c r="K98" t="s">
+        <v>30</v>
+      </c>
+      <c r="L98" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E99" t="s">
         <v>27</v>
       </c>
-      <c r="H94" t="s">
-        <v>35</v>
-      </c>
-      <c r="I94">
-        <v>10</v>
-      </c>
-      <c r="J94" t="s">
-        <v>22</v>
-      </c>
-      <c r="K94" t="s">
+      <c r="G99" t="s">
+        <v>33</v>
+      </c>
+      <c r="H99" t="s">
+        <v>31</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99" t="s">
+        <v>22</v>
+      </c>
+      <c r="K99" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H96" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I96" s="1">
-        <v>0</v>
-      </c>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H97" s="1" t="s">
+      <c r="L99" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E100" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" t="s">
+        <v>34</v>
+      </c>
+      <c r="H100" t="s">
         <v>31</v>
       </c>
-      <c r="I97" s="1">
-        <v>0</v>
-      </c>
-      <c r="J97" s="1"/>
-      <c r="K97" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H98" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I98" s="1">
-        <v>0</v>
-      </c>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
+      <c r="I100">
+        <v>0.3</v>
+      </c>
+      <c r="J100" t="s">
+        <v>22</v>
+      </c>
+      <c r="K100" t="s">
+        <v>59</v>
+      </c>
+      <c r="L100" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>1</v>
-      </c>
-      <c r="C101" t="s">
-        <v>2</v>
-      </c>
-      <c r="D101" t="s">
-        <v>3</v>
+      <c r="E101" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" t="s">
+        <v>34</v>
       </c>
       <c r="H101" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I101">
-        <v>5.39</v>
+        <v>30</v>
       </c>
       <c r="J101" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="K101" t="s">
+        <v>59</v>
       </c>
       <c r="L101" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>1</v>
-      </c>
-      <c r="C102" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102" t="s">
-        <v>3</v>
+      <c r="E102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G102" t="s">
+        <v>34</v>
       </c>
       <c r="H102" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I102">
-        <v>2.8</v>
+        <v>30</v>
       </c>
       <c r="J102" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K102" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="L102" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1</v>
       </c>
-      <c r="D103" t="s">
-        <v>13</v>
+      <c r="E103" t="s">
+        <v>25</v>
       </c>
       <c r="H103" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I103">
-        <v>2.2599999999999998</v>
+        <v>60</v>
       </c>
       <c r="J103" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="K103" t="s">
+        <v>30</v>
       </c>
       <c r="L103" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1</v>
       </c>
+      <c r="C104" t="s">
+        <v>2</v>
+      </c>
       <c r="D104" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="E104" t="s">
+        <v>26</v>
       </c>
       <c r="H104" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I104">
-        <v>0.79</v>
+        <v>51</v>
       </c>
       <c r="J104" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K104" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L104" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1</v>
       </c>
+      <c r="C105" t="s">
+        <v>9</v>
+      </c>
       <c r="D105" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="E105" t="s">
+        <v>26</v>
       </c>
       <c r="H105" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I105">
-        <v>2.2599999999999998</v>
+        <v>52</v>
       </c>
       <c r="J105" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="K105" t="s">
+        <v>30</v>
       </c>
       <c r="L105" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,19 +3685,25 @@
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>26</v>
       </c>
       <c r="H106" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I106">
-        <v>2.2599999999999998</v>
+        <v>51</v>
       </c>
       <c r="J106" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="K106" t="s">
+        <v>30</v>
       </c>
       <c r="L106" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -3564,18 +3711,412 @@
         <v>1</v>
       </c>
       <c r="D107" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s">
+        <v>26</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107">
+        <v>51</v>
+      </c>
+      <c r="J107" t="s">
+        <v>22</v>
+      </c>
+      <c r="K107" t="s">
+        <v>30</v>
+      </c>
+      <c r="L107" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1</v>
+      </c>
+      <c r="D108" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" t="s">
+        <v>26</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108">
+        <v>52</v>
+      </c>
+      <c r="J108" t="s">
+        <v>22</v>
+      </c>
+      <c r="K108" t="s">
+        <v>30</v>
+      </c>
+      <c r="L108" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1</v>
+      </c>
+      <c r="D109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" t="s">
+        <v>26</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109">
+        <v>52</v>
+      </c>
+      <c r="J109" t="s">
+        <v>22</v>
+      </c>
+      <c r="K109" t="s">
+        <v>30</v>
+      </c>
+      <c r="L109" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1</v>
+      </c>
+      <c r="D110" t="s">
         <v>18</v>
       </c>
-      <c r="H107" t="s">
+      <c r="E110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110">
+        <v>52</v>
+      </c>
+      <c r="J110" t="s">
+        <v>22</v>
+      </c>
+      <c r="K110" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>10</v>
+      </c>
+      <c r="J111" t="s">
+        <v>22</v>
+      </c>
+      <c r="K111" t="s">
+        <v>30</v>
+      </c>
+      <c r="L111" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>68</v>
+      </c>
+      <c r="C112" t="s">
+        <v>69</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112">
+        <v>40</v>
+      </c>
+      <c r="J112" t="s">
+        <v>22</v>
+      </c>
+      <c r="K112" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>45</v>
+      </c>
+      <c r="E113" t="s">
+        <v>25</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113">
+        <v>70</v>
+      </c>
+      <c r="J113" t="s">
+        <v>22</v>
+      </c>
+      <c r="K113" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>45</v>
+      </c>
+      <c r="E114" t="s">
+        <v>26</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114">
+        <v>51</v>
+      </c>
+      <c r="J114" t="s">
+        <v>22</v>
+      </c>
+      <c r="K114" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>45</v>
+      </c>
+      <c r="E115" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115">
+        <v>10</v>
+      </c>
+      <c r="J115" t="s">
+        <v>22</v>
+      </c>
+      <c r="K115" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H117" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I117" s="1">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H118" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I118" s="1">
+        <v>0</v>
+      </c>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H119" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119" s="1">
+        <v>0</v>
+      </c>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="3"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>3</v>
+      </c>
+      <c r="H122" t="s">
         <v>4</v>
       </c>
-      <c r="I107">
+      <c r="I122">
+        <v>5.39</v>
+      </c>
+      <c r="J122" t="s">
+        <v>5</v>
+      </c>
+      <c r="L122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>3</v>
+      </c>
+      <c r="H123" t="s">
+        <v>4</v>
+      </c>
+      <c r="I123">
+        <v>2.8</v>
+      </c>
+      <c r="J123" t="s">
+        <v>5</v>
+      </c>
+      <c r="K123" t="s">
+        <v>10</v>
+      </c>
+      <c r="L123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1</v>
+      </c>
+      <c r="D124" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" t="s">
+        <v>4</v>
+      </c>
+      <c r="I124">
         <v>2.2599999999999998</v>
       </c>
-      <c r="J107" t="s">
+      <c r="J124" t="s">
         <v>5</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1</v>
+      </c>
+      <c r="D125" t="s">
+        <v>14</v>
+      </c>
+      <c r="H125" t="s">
+        <v>4</v>
+      </c>
+      <c r="I125">
+        <v>0.79</v>
+      </c>
+      <c r="J125" t="s">
+        <v>5</v>
+      </c>
+      <c r="K125" t="s">
+        <v>15</v>
+      </c>
+      <c r="L125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1</v>
+      </c>
+      <c r="D126" t="s">
+        <v>17</v>
+      </c>
+      <c r="H126" t="s">
+        <v>4</v>
+      </c>
+      <c r="I126">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J126" t="s">
+        <v>5</v>
+      </c>
+      <c r="L126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1</v>
+      </c>
+      <c r="D127" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127" t="s">
+        <v>4</v>
+      </c>
+      <c r="I127">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J127" t="s">
+        <v>5</v>
+      </c>
+      <c r="L127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1</v>
+      </c>
+      <c r="D128" t="s">
+        <v>18</v>
+      </c>
+      <c r="H128" t="s">
+        <v>4</v>
+      </c>
+      <c r="I128">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J128" t="s">
+        <v>5</v>
+      </c>
+      <c r="K128" t="s">
         <v>19</v>
       </c>
     </row>

--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\prod_parameters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="82">
   <si>
     <t>value</t>
   </si>
@@ -241,6 +241,30 @@
   </si>
   <si>
     <t>of total N, assume same as laying hens for parent animals</t>
+  </si>
+  <si>
+    <t>horses</t>
+  </si>
+  <si>
+    <t>NIR 2022 Table 5.10</t>
+  </si>
+  <si>
+    <t>NIR 2022 Table 5.11</t>
+  </si>
+  <si>
+    <t>NIR 2022 Table 5.12</t>
+  </si>
+  <si>
+    <t>Remaining is grazing??</t>
+  </si>
+  <si>
+    <t>Same as cattle??</t>
+  </si>
+  <si>
+    <t>Same as cattle?? 17% is approx. avg. for cattle</t>
+  </si>
+  <si>
+    <t>Same as cattle?? 52% is approx. avg. for cattle</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1827,40 +1851,37 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H31" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="1">
+        <f>100-I32-I33-I34</f>
+        <v>65</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L31" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s">
         <v>21</v>
@@ -1871,83 +1892,71 @@
       <c r="J32" t="s">
         <v>22</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H33" t="s">
         <v>21</v>
       </c>
       <c r="I33">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="J33" t="s">
         <v>22</v>
       </c>
-      <c r="K33" t="s">
-        <v>49</v>
-      </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H34" t="s">
         <v>21</v>
       </c>
       <c r="I34">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="J34" t="s">
         <v>22</v>
       </c>
-      <c r="K34" t="s">
-        <v>48</v>
-      </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>45</v>
       </c>
-      <c r="D35" t="s">
-        <v>47</v>
+      <c r="B35" t="s">
+        <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
         <v>21</v>
       </c>
       <c r="I35">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="J35" t="s">
         <v>22</v>
       </c>
-      <c r="K35" t="s">
-        <v>48</v>
+      <c r="K35" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L35" t="s">
         <v>23</v>
@@ -1957,20 +1966,23 @@
       <c r="A36" t="s">
         <v>45</v>
       </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H36" t="s">
         <v>21</v>
       </c>
       <c r="I36">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J36" t="s">
         <v>22</v>
       </c>
-      <c r="K36" t="s">
-        <v>49</v>
+      <c r="K36" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L36" t="s">
         <v>23</v>
@@ -1980,23 +1992,20 @@
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="D37" t="s">
-        <v>46</v>
-      </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H37" t="s">
         <v>21</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
       </c>
       <c r="K37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L37" t="s">
         <v>23</v>
@@ -2007,16 +2016,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H38" t="s">
         <v>21</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="J38" t="s">
         <v>22</v>
@@ -2032,20 +2041,23 @@
       <c r="A39" t="s">
         <v>45</v>
       </c>
+      <c r="D39" t="s">
+        <v>47</v>
+      </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s">
         <v>21</v>
       </c>
       <c r="I39">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
       </c>
       <c r="K39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L39" t="s">
         <v>23</v>
@@ -2055,23 +2067,20 @@
       <c r="A40" t="s">
         <v>45</v>
       </c>
-      <c r="D40" t="s">
-        <v>46</v>
-      </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H40" t="s">
         <v>21</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L40" t="s">
         <v>23</v>
@@ -2082,16 +2091,16 @@
         <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H41" t="s">
         <v>21</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="s">
         <v>22</v>
@@ -2105,91 +2114,103 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H42" t="s">
         <v>21</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
+      </c>
+      <c r="K42" t="s">
+        <v>48</v>
+      </c>
+      <c r="L42" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
+        <v>27</v>
+      </c>
+      <c r="H43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43">
         <v>20</v>
       </c>
-      <c r="H43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
       <c r="J43" t="s">
         <v>22</v>
+      </c>
+      <c r="K43" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H44" t="s">
         <v>21</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
+      </c>
+      <c r="K44" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
-      </c>
-      <c r="C45" t="s">
-        <v>69</v>
+        <v>45</v>
+      </c>
+      <c r="D45" t="s">
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H45" t="s">
         <v>21</v>
       </c>
       <c r="I45">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
       </c>
       <c r="K45" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="L45" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2203,7 +2224,7 @@
         <v>70</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
         <v>21</v>
@@ -2223,19 +2244,16 @@
         <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
         <v>21</v>
       </c>
       <c r="I47">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
-      </c>
-      <c r="K47" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2249,13 +2267,13 @@
         <v>70</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H48" t="s">
         <v>21</v>
       </c>
       <c r="I48">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -2269,13 +2287,13 @@
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H49" t="s">
         <v>21</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
@@ -2284,140 +2302,152 @@
         <v>72</v>
       </c>
     </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51">
+        <v>86</v>
+      </c>
+      <c r="J51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K51" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>3</v>
+        <v>70</v>
+      </c>
+      <c r="E52" t="s">
+        <v>27</v>
       </c>
       <c r="H52" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I52">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="J52" t="s">
-        <v>8</v>
-      </c>
-      <c r="L52" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" t="s">
-        <v>3</v>
+        <v>69</v>
+      </c>
+      <c r="E53" t="s">
+        <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I53">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="J53" t="s">
-        <v>8</v>
-      </c>
-      <c r="L53" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
-        <v>13</v>
-      </c>
-      <c r="H54" t="s">
-        <v>7</v>
-      </c>
-      <c r="I54">
-        <v>47</v>
-      </c>
-      <c r="J54" t="s">
-        <v>8</v>
-      </c>
-      <c r="L54" t="s">
-        <v>12</v>
+        <v>22</v>
+      </c>
+      <c r="K53" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s">
-        <v>7</v>
-      </c>
-      <c r="I55">
-        <v>28</v>
-      </c>
-      <c r="J55" t="s">
-        <v>8</v>
-      </c>
-      <c r="L55" t="s">
-        <v>12</v>
-      </c>
+      <c r="A55" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1</v>
       </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H56" t="s">
         <v>7</v>
       </c>
       <c r="I56">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="J56" t="s">
         <v>8</v>
       </c>
       <c r="L56" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1</v>
       </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
       <c r="D57" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H57" t="s">
         <v>7</v>
       </c>
       <c r="I57">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="J57" t="s">
         <v>8</v>
@@ -2431,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H58" t="s">
         <v>7</v>
@@ -2442,25 +2472,22 @@
       <c r="J58" t="s">
         <v>8</v>
       </c>
-      <c r="K58" t="s">
-        <v>19</v>
-      </c>
       <c r="L58" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
         <v>7</v>
       </c>
       <c r="I59">
-        <v>22.5</v>
+        <v>28</v>
       </c>
       <c r="J59" t="s">
         <v>8</v>
@@ -2471,16 +2498,16 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="H60" t="s">
         <v>7</v>
       </c>
       <c r="I60">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="J60" t="s">
         <v>8</v>
@@ -2491,45 +2518,42 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
         <v>7</v>
       </c>
       <c r="I61">
-        <v>1.2</v>
+        <v>47</v>
       </c>
       <c r="J61" t="s">
         <v>8</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="L61" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
         <v>7</v>
       </c>
       <c r="I62">
-        <v>9.5</v>
+        <v>47</v>
       </c>
       <c r="J62" t="s">
         <v>8</v>
       </c>
       <c r="K62" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="L62" t="s">
         <v>12</v>
@@ -2537,22 +2561,16 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>45</v>
-      </c>
-      <c r="D63" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s">
         <v>7</v>
       </c>
       <c r="I63">
-        <v>9.5</v>
+        <v>48</v>
       </c>
       <c r="J63" t="s">
         <v>8</v>
-      </c>
-      <c r="K63" t="s">
-        <v>57</v>
       </c>
       <c r="L63" t="s">
         <v>12</v>
@@ -2563,39 +2581,33 @@
         <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H64" t="s">
         <v>7</v>
       </c>
       <c r="I64">
-        <v>9.5</v>
+        <v>22.5</v>
       </c>
       <c r="J64" t="s">
         <v>8</v>
       </c>
-      <c r="K64" t="s">
-        <v>57</v>
-      </c>
       <c r="L64" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="H65" t="s">
         <v>7</v>
       </c>
       <c r="I65">
-        <v>0.28999999999999998</v>
+        <v>13</v>
       </c>
       <c r="J65" t="s">
         <v>8</v>
@@ -2606,22 +2618,22 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66" t="s">
-        <v>69</v>
+        <v>45</v>
+      </c>
+      <c r="D66" t="s">
+        <v>54</v>
       </c>
       <c r="H66" t="s">
         <v>7</v>
       </c>
       <c r="I66">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="s">
         <v>8</v>
       </c>
-      <c r="K66" t="s">
-        <v>71</v>
+      <c r="K66" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="L66" t="s">
         <v>12</v>
@@ -2629,140 +2641,125 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D67" t="s">
+        <v>55</v>
       </c>
       <c r="H67" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="J67" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K67" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="L67" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D68" t="s">
+        <v>46</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="J68" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K68" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
-        <v>27</v>
-      </c>
-      <c r="G69" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="D69" t="s">
+        <v>47</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I69">
-        <v>20</v>
+        <v>9.5</v>
       </c>
       <c r="J69" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K69" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="L69" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>45</v>
-      </c>
-      <c r="E70" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" t="s">
-        <v>28</v>
+        <v>68</v>
+      </c>
+      <c r="C70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>70</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I70">
-        <v>10</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J70" t="s">
-        <v>22</v>
-      </c>
-      <c r="K70" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>45</v>
-      </c>
-      <c r="E71" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" t="s">
-        <v>28</v>
+        <v>68</v>
+      </c>
+      <c r="C71" t="s">
+        <v>69</v>
       </c>
       <c r="H71" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I71">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K71" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="L71" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G72" t="s">
         <v>28</v>
@@ -2771,7 +2768,7 @@
         <v>29</v>
       </c>
       <c r="I72">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -2785,16 +2782,10 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
-      </c>
-      <c r="C73" t="s">
-        <v>69</v>
-      </c>
-      <c r="D73" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G73" t="s">
         <v>28</v>
@@ -2803,7 +2794,7 @@
         <v>29</v>
       </c>
       <c r="I73">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -2817,13 +2808,10 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>68</v>
-      </c>
-      <c r="C74" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G74" t="s">
         <v>28</v>
@@ -2832,13 +2820,13 @@
         <v>29</v>
       </c>
       <c r="I74">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
       </c>
       <c r="K74" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="L74" t="s">
         <v>23</v>
@@ -2846,13 +2834,10 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>68</v>
-      </c>
-      <c r="C75" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G75" t="s">
         <v>28</v>
@@ -2867,7 +2852,7 @@
         <v>22</v>
       </c>
       <c r="K75" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="L75" t="s">
         <v>23</v>
@@ -2875,13 +2860,10 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>68</v>
-      </c>
-      <c r="C76" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G76" t="s">
         <v>28</v>
@@ -2890,13 +2872,13 @@
         <v>29</v>
       </c>
       <c r="I76">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J76" t="s">
         <v>22</v>
       </c>
       <c r="K76" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="L76" t="s">
         <v>23</v>
@@ -2904,19 +2886,19 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G77" t="s">
         <v>28</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -2930,25 +2912,25 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="D78" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="E78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G78" t="s">
         <v>28</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I78">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
@@ -2962,31 +2944,28 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="E79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G79" t="s">
         <v>28</v>
       </c>
       <c r="H79" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I79">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
       </c>
       <c r="K79" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L79" t="s">
         <v>23</v>
@@ -2994,10 +2973,10 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1</v>
-      </c>
-      <c r="D80" t="s">
-        <v>13</v>
+        <v>68</v>
+      </c>
+      <c r="C80" t="s">
+        <v>69</v>
       </c>
       <c r="E80" t="s">
         <v>26</v>
@@ -3006,16 +2985,16 @@
         <v>28</v>
       </c>
       <c r="H80" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I80">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
       </c>
       <c r="K80" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L80" t="s">
         <v>23</v>
@@ -3023,118 +3002,112 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C81" t="s">
+        <v>69</v>
       </c>
       <c r="E81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G81" t="s">
         <v>28</v>
       </c>
       <c r="H81" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I81">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
       </c>
       <c r="K81" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L81" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
-        <v>16</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="A82" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I82" s="1">
+        <v>4</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G82" t="s">
+      <c r="F83" s="1"/>
+      <c r="G83" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H82" t="s">
-        <v>31</v>
-      </c>
-      <c r="I82">
-        <v>17</v>
-      </c>
-      <c r="J82" t="s">
-        <v>22</v>
-      </c>
-      <c r="K82" t="s">
-        <v>30</v>
-      </c>
-      <c r="L82" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="H83" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I83" s="1">
+        <v>4</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H83" t="s">
-        <v>31</v>
-      </c>
-      <c r="I83">
-        <v>17</v>
-      </c>
-      <c r="J83" t="s">
-        <v>22</v>
-      </c>
-      <c r="K83" t="s">
-        <v>30</v>
-      </c>
-      <c r="L83" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" t="s">
-        <v>26</v>
-      </c>
-      <c r="G84" t="s">
-        <v>28</v>
-      </c>
-      <c r="H84" t="s">
-        <v>31</v>
-      </c>
-      <c r="I84">
-        <v>17</v>
-      </c>
-      <c r="J84" t="s">
-        <v>22</v>
-      </c>
-      <c r="K84" t="s">
-        <v>67</v>
-      </c>
-      <c r="L84" t="s">
-        <v>23</v>
+      <c r="H84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I84" s="1">
+        <v>20</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3142,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G85" t="s">
         <v>28</v>
@@ -3151,7 +3124,7 @@
         <v>31</v>
       </c>
       <c r="I85">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J85" t="s">
         <v>22</v>
@@ -3165,10 +3138,16 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" t="s">
+        <v>3</v>
       </c>
       <c r="E86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G86" t="s">
         <v>28</v>
@@ -3177,7 +3156,7 @@
         <v>31</v>
       </c>
       <c r="I86">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J86" t="s">
         <v>22</v>
@@ -3191,7 +3170,13 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" t="s">
+        <v>3</v>
       </c>
       <c r="E87" t="s">
         <v>26</v>
@@ -3203,7 +3188,7 @@
         <v>31</v>
       </c>
       <c r="I87">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
@@ -3217,10 +3202,13 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G88" t="s">
         <v>28</v>
@@ -3229,7 +3217,7 @@
         <v>31</v>
       </c>
       <c r="I88">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J88" t="s">
         <v>22</v>
@@ -3243,13 +3231,10 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>68</v>
-      </c>
-      <c r="C89" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="E89" t="s">
         <v>26</v>
@@ -3261,7 +3246,7 @@
         <v>31</v>
       </c>
       <c r="I89">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J89" t="s">
         <v>22</v>
@@ -3275,16 +3260,13 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>68</v>
-      </c>
-      <c r="C90" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G90" t="s">
         <v>28</v>
@@ -3293,7 +3275,7 @@
         <v>31</v>
       </c>
       <c r="I90">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J90" t="s">
         <v>22</v>
@@ -3307,13 +3289,13 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>68</v>
-      </c>
-      <c r="C91" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
+        <v>17</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G91" t="s">
         <v>28</v>
@@ -3322,13 +3304,13 @@
         <v>31</v>
       </c>
       <c r="I91">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J91" t="s">
         <v>22</v>
       </c>
       <c r="K91" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="L91" t="s">
         <v>23</v>
@@ -3336,10 +3318,10 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>68</v>
-      </c>
-      <c r="C92" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>18</v>
       </c>
       <c r="E92" t="s">
         <v>26</v>
@@ -3351,13 +3333,13 @@
         <v>31</v>
       </c>
       <c r="I92">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J92" t="s">
         <v>22</v>
       </c>
       <c r="K92" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L92" t="s">
         <v>23</v>
@@ -3365,10 +3347,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>68</v>
-      </c>
-      <c r="C93" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3380,99 +3359,114 @@
         <v>31</v>
       </c>
       <c r="I93">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J93" t="s">
         <v>22</v>
       </c>
       <c r="K93" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="L93" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E94" t="s">
+      <c r="A94" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G94" t="s">
-        <v>32</v>
-      </c>
-      <c r="H94" t="s">
+      <c r="F94" s="1"/>
+      <c r="G94" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I94">
-        <v>0.01</v>
-      </c>
-      <c r="J94" t="s">
-        <v>22</v>
-      </c>
-      <c r="K94" t="s">
-        <v>59</v>
-      </c>
-      <c r="L94" t="s">
-        <v>23</v>
+      <c r="I94" s="1">
+        <v>3</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E95" t="s">
+      <c r="A95" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G95" t="s">
-        <v>32</v>
-      </c>
-      <c r="H95" t="s">
+      <c r="F95" s="1"/>
+      <c r="G95" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H95" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I95">
-        <v>1</v>
-      </c>
-      <c r="J95" t="s">
-        <v>22</v>
-      </c>
-      <c r="K95" t="s">
-        <v>59</v>
-      </c>
-      <c r="L95" t="s">
-        <v>23</v>
+      <c r="I95" s="1">
+        <v>17</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E96" t="s">
+      <c r="A96" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G96" t="s">
-        <v>32</v>
-      </c>
-      <c r="H96" t="s">
+      <c r="F96" s="1"/>
+      <c r="G96" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H96" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96" t="s">
-        <v>22</v>
-      </c>
-      <c r="K96" t="s">
-        <v>59</v>
-      </c>
-      <c r="L96" t="s">
-        <v>23</v>
+      <c r="I96" s="1">
+        <v>30</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>45</v>
+      </c>
       <c r="E97" t="s">
         <v>25</v>
       </c>
       <c r="G97" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H97" t="s">
         <v>31</v>
       </c>
       <c r="I97">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J97" t="s">
         <v>22</v>
@@ -3485,17 +3479,20 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>45</v>
+      </c>
       <c r="E98" t="s">
         <v>26</v>
       </c>
       <c r="G98" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H98" t="s">
         <v>31</v>
       </c>
       <c r="I98">
-        <v>0.5</v>
+        <v>18</v>
       </c>
       <c r="J98" t="s">
         <v>22</v>
@@ -3508,17 +3505,20 @@
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>45</v>
+      </c>
       <c r="E99" t="s">
         <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H99" t="s">
         <v>31</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J99" t="s">
         <v>22</v>
@@ -3531,69 +3531,93 @@
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>68</v>
+      </c>
+      <c r="C100" t="s">
+        <v>69</v>
+      </c>
+      <c r="D100" t="s">
+        <v>70</v>
+      </c>
       <c r="E100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G100" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H100" t="s">
         <v>31</v>
       </c>
       <c r="I100">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="J100" t="s">
         <v>22</v>
       </c>
       <c r="K100" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="L100" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>68</v>
+      </c>
+      <c r="C101" t="s">
+        <v>69</v>
+      </c>
+      <c r="D101" t="s">
+        <v>70</v>
+      </c>
       <c r="E101" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H101" t="s">
         <v>31</v>
       </c>
       <c r="I101">
+        <v>5</v>
+      </c>
+      <c r="J101" t="s">
+        <v>22</v>
+      </c>
+      <c r="K101" t="s">
         <v>30</v>
       </c>
-      <c r="J101" t="s">
-        <v>22</v>
-      </c>
-      <c r="K101" t="s">
-        <v>59</v>
-      </c>
       <c r="L101" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>68</v>
+      </c>
+      <c r="C102" t="s">
+        <v>69</v>
+      </c>
       <c r="E102" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H102" t="s">
         <v>31</v>
       </c>
       <c r="I102">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="J102" t="s">
         <v>22</v>
       </c>
       <c r="K102" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="L102" t="s">
         <v>23</v>
@@ -3601,22 +3625,28 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="C103" t="s">
+        <v>69</v>
       </c>
       <c r="E103" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G103" t="s">
+        <v>28</v>
       </c>
       <c r="H103" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I103">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="J103" t="s">
         <v>22</v>
       </c>
       <c r="K103" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L103" t="s">
         <v>23</v>
@@ -3624,129 +3654,114 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D104" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="E104" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="G104" t="s">
+        <v>28</v>
       </c>
       <c r="H104" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I104">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="J104" t="s">
         <v>22</v>
       </c>
       <c r="K104" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="L104" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>1</v>
-      </c>
-      <c r="C105" t="s">
-        <v>9</v>
-      </c>
-      <c r="D105" t="s">
-        <v>3</v>
-      </c>
       <c r="E105" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="G105" t="s">
+        <v>32</v>
       </c>
       <c r="H105" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I105">
-        <v>52</v>
+        <v>0.01</v>
       </c>
       <c r="J105" t="s">
         <v>22</v>
       </c>
       <c r="K105" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="L105" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>1</v>
-      </c>
-      <c r="D106" t="s">
-        <v>13</v>
-      </c>
       <c r="E106" t="s">
         <v>26</v>
       </c>
+      <c r="G106" t="s">
+        <v>32</v>
+      </c>
       <c r="H106" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I106">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="J106" t="s">
         <v>22</v>
       </c>
       <c r="K106" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="L106" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>1</v>
-      </c>
-      <c r="D107" t="s">
-        <v>14</v>
-      </c>
       <c r="E107" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="G107" t="s">
+        <v>32</v>
       </c>
       <c r="H107" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I107">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="J107" t="s">
         <v>22</v>
       </c>
       <c r="K107" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="L107" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>1</v>
-      </c>
-      <c r="D108" t="s">
-        <v>16</v>
-      </c>
       <c r="E108" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="G108" t="s">
+        <v>33</v>
       </c>
       <c r="H108" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I108">
-        <v>52</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="s">
         <v>22</v>
@@ -3759,20 +3774,17 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>1</v>
-      </c>
-      <c r="D109" t="s">
-        <v>17</v>
-      </c>
       <c r="E109" t="s">
         <v>26</v>
       </c>
+      <c r="G109" t="s">
+        <v>33</v>
+      </c>
       <c r="H109" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I109">
-        <v>52</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="s">
         <v>22</v>
@@ -3785,103 +3797,109 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>1</v>
-      </c>
-      <c r="D110" t="s">
-        <v>18</v>
-      </c>
       <c r="E110" t="s">
+        <v>27</v>
+      </c>
+      <c r="G110" t="s">
+        <v>33</v>
+      </c>
+      <c r="H110" t="s">
+        <v>31</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110" t="s">
+        <v>22</v>
+      </c>
+      <c r="K110" t="s">
+        <v>30</v>
+      </c>
+      <c r="L110" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E111" t="s">
+        <v>25</v>
+      </c>
+      <c r="G111" t="s">
+        <v>34</v>
+      </c>
+      <c r="H111" t="s">
+        <v>31</v>
+      </c>
+      <c r="I111">
+        <v>0.3</v>
+      </c>
+      <c r="J111" t="s">
+        <v>22</v>
+      </c>
+      <c r="K111" t="s">
+        <v>59</v>
+      </c>
+      <c r="L111" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E112" t="s">
         <v>26</v>
       </c>
-      <c r="H110" t="s">
-        <v>35</v>
-      </c>
-      <c r="I110">
-        <v>52</v>
-      </c>
-      <c r="J110" t="s">
-        <v>22</v>
-      </c>
-      <c r="K110" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>1</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="G112" t="s">
+        <v>34</v>
+      </c>
+      <c r="H112" t="s">
+        <v>31</v>
+      </c>
+      <c r="I112">
+        <v>30</v>
+      </c>
+      <c r="J112" t="s">
+        <v>22</v>
+      </c>
+      <c r="K112" t="s">
+        <v>59</v>
+      </c>
+      <c r="L112" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E113" t="s">
         <v>27</v>
       </c>
-      <c r="H111" t="s">
-        <v>35</v>
-      </c>
-      <c r="I111">
-        <v>10</v>
-      </c>
-      <c r="J111" t="s">
-        <v>22</v>
-      </c>
-      <c r="K111" t="s">
+      <c r="G113" t="s">
+        <v>34</v>
+      </c>
+      <c r="H113" t="s">
+        <v>31</v>
+      </c>
+      <c r="I113">
         <v>30</v>
       </c>
-      <c r="L111" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>68</v>
-      </c>
-      <c r="C112" t="s">
-        <v>69</v>
-      </c>
-      <c r="H112" t="s">
-        <v>35</v>
-      </c>
-      <c r="I112">
-        <v>40</v>
-      </c>
-      <c r="J112" t="s">
-        <v>22</v>
-      </c>
-      <c r="K112" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>45</v>
-      </c>
-      <c r="E113" t="s">
-        <v>25</v>
-      </c>
-      <c r="H113" t="s">
-        <v>35</v>
-      </c>
-      <c r="I113">
-        <v>70</v>
-      </c>
       <c r="J113" t="s">
         <v>22</v>
       </c>
       <c r="K113" t="s">
-        <v>30</v>
+        <v>59</v>
+      </c>
+      <c r="L113" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H114" t="s">
         <v>35</v>
       </c>
       <c r="I114">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J114" t="s">
         <v>22</v>
@@ -3889,19 +3907,28 @@
       <c r="K114" t="s">
         <v>30</v>
       </c>
+      <c r="L114" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>3</v>
       </c>
       <c r="E115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H115" t="s">
         <v>35</v>
       </c>
       <c r="I115">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="J115" t="s">
         <v>22</v>
@@ -3909,214 +3936,551 @@
       <c r="K115" t="s">
         <v>30</v>
       </c>
+      <c r="L115" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" t="s">
+        <v>3</v>
+      </c>
+      <c r="E116" t="s">
+        <v>26</v>
+      </c>
+      <c r="H116" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116">
+        <v>52</v>
+      </c>
+      <c r="J116" t="s">
+        <v>22</v>
+      </c>
+      <c r="K116" t="s">
+        <v>30</v>
+      </c>
+      <c r="L116" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H117" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I117" s="1">
-        <v>0</v>
-      </c>
-      <c r="J117" s="1"/>
-      <c r="K117" s="1" t="s">
-        <v>66</v>
+      <c r="A117" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>26</v>
+      </c>
+      <c r="H117" t="s">
+        <v>35</v>
+      </c>
+      <c r="I117">
+        <v>51</v>
+      </c>
+      <c r="J117" t="s">
+        <v>22</v>
+      </c>
+      <c r="K117" t="s">
+        <v>30</v>
+      </c>
+      <c r="L117" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H118" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I118" s="1">
-        <v>0</v>
-      </c>
-      <c r="J118" s="1"/>
-      <c r="K118" s="1" t="s">
-        <v>66</v>
+      <c r="A118" t="s">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" t="s">
+        <v>26</v>
+      </c>
+      <c r="H118" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118">
+        <v>51</v>
+      </c>
+      <c r="J118" t="s">
+        <v>22</v>
+      </c>
+      <c r="K118" t="s">
+        <v>30</v>
+      </c>
+      <c r="L118" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H119" s="1" t="s">
+      <c r="A119" t="s">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" t="s">
+        <v>26</v>
+      </c>
+      <c r="H119" t="s">
         <v>35</v>
       </c>
-      <c r="I119" s="1">
-        <v>0</v>
-      </c>
-      <c r="J119" s="1"/>
-      <c r="K119" s="1" t="s">
-        <v>66</v>
+      <c r="I119">
+        <v>52</v>
+      </c>
+      <c r="J119" t="s">
+        <v>22</v>
+      </c>
+      <c r="K119" t="s">
+        <v>30</v>
+      </c>
+      <c r="L119" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1"/>
-      <c r="K120" s="1"/>
+      <c r="A120" t="s">
+        <v>1</v>
+      </c>
+      <c r="D120" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" t="s">
+        <v>26</v>
+      </c>
+      <c r="H120" t="s">
+        <v>35</v>
+      </c>
+      <c r="I120">
+        <v>52</v>
+      </c>
+      <c r="J120" t="s">
+        <v>22</v>
+      </c>
+      <c r="K120" t="s">
+        <v>30</v>
+      </c>
+      <c r="L120" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="3"/>
-      <c r="J121" s="3"/>
-      <c r="K121" s="3"/>
-      <c r="L121" s="3"/>
+      <c r="A121" t="s">
+        <v>1</v>
+      </c>
+      <c r="D121" t="s">
+        <v>18</v>
+      </c>
+      <c r="E121" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121">
+        <v>52</v>
+      </c>
+      <c r="J121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K121" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1</v>
       </c>
-      <c r="C122" t="s">
-        <v>2</v>
-      </c>
-      <c r="D122" t="s">
-        <v>3</v>
+      <c r="E122" t="s">
+        <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I122">
-        <v>5.39</v>
+        <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="K122" t="s">
+        <v>30</v>
       </c>
       <c r="L122" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>1</v>
-      </c>
-      <c r="C123" t="s">
-        <v>9</v>
-      </c>
-      <c r="D123" t="s">
-        <v>3</v>
-      </c>
-      <c r="H123" t="s">
-        <v>4</v>
-      </c>
-      <c r="I123">
-        <v>2.8</v>
-      </c>
-      <c r="J123" t="s">
-        <v>5</v>
-      </c>
-      <c r="K123" t="s">
+      <c r="A123" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123" s="1">
+        <v>60</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I124" s="1">
+        <v>52</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125" s="1">
         <v>10</v>
       </c>
-      <c r="L123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>1</v>
-      </c>
-      <c r="D124" t="s">
-        <v>13</v>
-      </c>
-      <c r="H124" t="s">
-        <v>4</v>
-      </c>
-      <c r="I124">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J124" t="s">
-        <v>5</v>
-      </c>
-      <c r="L124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>1</v>
-      </c>
-      <c r="D125" t="s">
-        <v>14</v>
-      </c>
-      <c r="H125" t="s">
-        <v>4</v>
-      </c>
-      <c r="I125">
-        <v>0.79</v>
-      </c>
-      <c r="J125" t="s">
-        <v>5</v>
-      </c>
-      <c r="K125" t="s">
-        <v>15</v>
-      </c>
-      <c r="L125" t="s">
-        <v>11</v>
+      <c r="J125" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1</v>
-      </c>
-      <c r="D126" t="s">
-        <v>17</v>
+        <v>68</v>
+      </c>
+      <c r="C126" t="s">
+        <v>69</v>
       </c>
       <c r="H126" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I126">
-        <v>2.2599999999999998</v>
+        <v>40</v>
       </c>
       <c r="J126" t="s">
-        <v>5</v>
-      </c>
-      <c r="L126" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="K126" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1</v>
-      </c>
-      <c r="D127" t="s">
-        <v>16</v>
+        <v>45</v>
+      </c>
+      <c r="E127" t="s">
+        <v>25</v>
       </c>
       <c r="H127" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I127">
-        <v>2.2599999999999998</v>
+        <v>70</v>
       </c>
       <c r="J127" t="s">
-        <v>5</v>
-      </c>
-      <c r="L127" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="K127" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1</v>
-      </c>
-      <c r="D128" t="s">
+        <v>45</v>
+      </c>
+      <c r="E128" t="s">
+        <v>26</v>
+      </c>
+      <c r="H128" t="s">
+        <v>35</v>
+      </c>
+      <c r="I128">
+        <v>51</v>
+      </c>
+      <c r="J128" t="s">
+        <v>22</v>
+      </c>
+      <c r="K128" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>45</v>
+      </c>
+      <c r="E129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129">
+        <v>10</v>
+      </c>
+      <c r="J129" t="s">
+        <v>22</v>
+      </c>
+      <c r="K129" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H131" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I131" s="1">
+        <v>0</v>
+      </c>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H132" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I132" s="1">
+        <v>0</v>
+      </c>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H133" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I133" s="1">
+        <v>0</v>
+      </c>
+      <c r="J133" s="1"/>
+      <c r="K133" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="3"/>
+      <c r="K135" s="3"/>
+      <c r="L135" s="3"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136" t="s">
+        <v>3</v>
+      </c>
+      <c r="H136" t="s">
+        <v>4</v>
+      </c>
+      <c r="I136">
+        <v>5.39</v>
+      </c>
+      <c r="J136" t="s">
+        <v>5</v>
+      </c>
+      <c r="L136" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" t="s">
+        <v>3</v>
+      </c>
+      <c r="H137" t="s">
+        <v>4</v>
+      </c>
+      <c r="I137">
+        <v>2.8</v>
+      </c>
+      <c r="J137" t="s">
+        <v>5</v>
+      </c>
+      <c r="K137" t="s">
+        <v>10</v>
+      </c>
+      <c r="L137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>1</v>
+      </c>
+      <c r="D138" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" t="s">
+        <v>4</v>
+      </c>
+      <c r="I138">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J138" t="s">
+        <v>5</v>
+      </c>
+      <c r="L138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>1</v>
+      </c>
+      <c r="D139" t="s">
+        <v>14</v>
+      </c>
+      <c r="H139" t="s">
+        <v>4</v>
+      </c>
+      <c r="I139">
+        <v>0.79</v>
+      </c>
+      <c r="J139" t="s">
+        <v>5</v>
+      </c>
+      <c r="K139" t="s">
+        <v>15</v>
+      </c>
+      <c r="L139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1</v>
+      </c>
+      <c r="D140" t="s">
+        <v>17</v>
+      </c>
+      <c r="H140" t="s">
+        <v>4</v>
+      </c>
+      <c r="I140">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J140" t="s">
+        <v>5</v>
+      </c>
+      <c r="L140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1</v>
+      </c>
+      <c r="D141" t="s">
+        <v>16</v>
+      </c>
+      <c r="H141" t="s">
+        <v>4</v>
+      </c>
+      <c r="I141">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J141" t="s">
+        <v>5</v>
+      </c>
+      <c r="L141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1</v>
+      </c>
+      <c r="D142" t="s">
         <v>18</v>
       </c>
-      <c r="H128" t="s">
+      <c r="H142" t="s">
         <v>4</v>
       </c>
-      <c r="I128">
+      <c r="I142">
         <v>2.2599999999999998</v>
       </c>
-      <c r="J128" t="s">
+      <c r="J142" t="s">
         <v>5</v>
       </c>
-      <c r="K128" t="s">
+      <c r="K142" t="s">
         <v>19</v>
       </c>
     </row>

--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="83">
   <si>
     <t>value</t>
   </si>
@@ -111,9 +111,6 @@
     <t>loss_stable</t>
   </si>
   <si>
-    <t>of total N</t>
-  </si>
-  <si>
     <t>loss_storage</t>
   </si>
   <si>
@@ -198,9 +195,6 @@
     <t>Definition mismatch? 20kg vs 30kg</t>
   </si>
   <si>
-    <t>of TAN</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
@@ -222,9 +216,6 @@
     <t>fallback OK?</t>
   </si>
   <si>
-    <t>of total N, Assume same as bulls</t>
-  </si>
-  <si>
     <t>poultry</t>
   </si>
   <si>
@@ -240,9 +231,6 @@
     <t>Assume same as laying hens for parent animals</t>
   </si>
   <si>
-    <t>of total N, assume same as laying hens for parent animals</t>
-  </si>
-  <si>
     <t>horses</t>
   </si>
   <si>
@@ -264,14 +252,29 @@
     <t>Same as cattle?? 17% is approx. avg. for cattle</t>
   </si>
   <si>
-    <t>Same as cattle?? 52% is approx. avg. for cattle</t>
+    <t>Swedish IIR 2019 Table 5-10</t>
+  </si>
+  <si>
+    <t>mammadjuren</t>
+  </si>
+  <si>
+    <t>% of total N</t>
+  </si>
+  <si>
+    <t>assume same as laying hens for parent animals</t>
+  </si>
+  <si>
+    <t>% of TAN</t>
+  </si>
+  <si>
+    <t>Assume same as solid manure</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +414,12 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -763,12 +772,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1090,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1106,45 +1116,45 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1852,7 +1862,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1873,12 +1883,12 @@
         <v>22</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
@@ -1893,12 +1903,12 @@
         <v>22</v>
       </c>
       <c r="L32" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
@@ -1913,12 +1923,12 @@
         <v>22</v>
       </c>
       <c r="L33" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -1933,15 +1943,15 @@
         <v>22</v>
       </c>
       <c r="L34" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
@@ -1956,7 +1966,7 @@
         <v>22</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L35" t="s">
         <v>23</v>
@@ -1964,10 +1974,10 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
@@ -1982,7 +1992,7 @@
         <v>22</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L36" t="s">
         <v>23</v>
@@ -1990,7 +2000,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
         <v>25</v>
@@ -2005,7 +2015,7 @@
         <v>22</v>
       </c>
       <c r="K37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L37" t="s">
         <v>23</v>
@@ -2013,10 +2023,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
         <v>45</v>
-      </c>
-      <c r="D38" t="s">
-        <v>46</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
@@ -2031,7 +2041,7 @@
         <v>22</v>
       </c>
       <c r="K38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L38" t="s">
         <v>23</v>
@@ -2039,10 +2049,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
@@ -2057,7 +2067,7 @@
         <v>22</v>
       </c>
       <c r="K39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L39" t="s">
         <v>23</v>
@@ -2065,7 +2075,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E40" t="s">
         <v>26</v>
@@ -2080,7 +2090,7 @@
         <v>22</v>
       </c>
       <c r="K40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L40" t="s">
         <v>23</v>
@@ -2088,10 +2098,10 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" t="s">
         <v>45</v>
-      </c>
-      <c r="D41" t="s">
-        <v>46</v>
       </c>
       <c r="E41" t="s">
         <v>26</v>
@@ -2106,7 +2116,7 @@
         <v>22</v>
       </c>
       <c r="K41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L41" t="s">
         <v>23</v>
@@ -2114,10 +2124,10 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E42" t="s">
         <v>26</v>
@@ -2132,7 +2142,7 @@
         <v>22</v>
       </c>
       <c r="K42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L42" t="s">
         <v>23</v>
@@ -2140,7 +2150,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2155,7 +2165,7 @@
         <v>22</v>
       </c>
       <c r="K43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L43" t="s">
         <v>23</v>
@@ -2163,10 +2173,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
         <v>45</v>
-      </c>
-      <c r="D44" t="s">
-        <v>46</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2181,7 +2191,7 @@
         <v>22</v>
       </c>
       <c r="K44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L44" t="s">
         <v>23</v>
@@ -2189,10 +2199,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2207,7 +2217,7 @@
         <v>22</v>
       </c>
       <c r="K45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L45" t="s">
         <v>23</v>
@@ -2215,13 +2225,13 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E46" t="s">
         <v>20</v>
@@ -2238,10 +2248,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E47" t="s">
         <v>20</v>
@@ -2258,13 +2268,13 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D48" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s">
         <v>25</v>
@@ -2281,10 +2291,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E49" t="s">
         <v>25</v>
@@ -2299,18 +2309,18 @@
         <v>22</v>
       </c>
       <c r="K49" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
         <v>26</v>
@@ -2327,10 +2337,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E51" t="s">
         <v>26</v>
@@ -2345,18 +2355,18 @@
         <v>22</v>
       </c>
       <c r="K51" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2373,10 +2383,10 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2391,12 +2401,12 @@
         <v>22</v>
       </c>
       <c r="K53" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2561,7 +2571,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H63" t="s">
         <v>7</v>
@@ -2578,10 +2588,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H64" t="s">
         <v>7</v>
@@ -2598,10 +2608,10 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H65" t="s">
         <v>7</v>
@@ -2618,10 +2628,10 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H66" t="s">
         <v>7</v>
@@ -2633,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L66" t="s">
         <v>12</v>
@@ -2641,10 +2651,10 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H67" t="s">
         <v>7</v>
@@ -2656,7 +2666,7 @@
         <v>8</v>
       </c>
       <c r="K67" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L67" t="s">
         <v>12</v>
@@ -2664,10 +2674,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" t="s">
         <v>45</v>
-      </c>
-      <c r="D68" t="s">
-        <v>46</v>
       </c>
       <c r="H68" t="s">
         <v>7</v>
@@ -2679,7 +2689,7 @@
         <v>8</v>
       </c>
       <c r="K68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L68" t="s">
         <v>12</v>
@@ -2687,10 +2697,10 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H69" t="s">
         <v>7</v>
@@ -2702,7 +2712,7 @@
         <v>8</v>
       </c>
       <c r="K69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L69" t="s">
         <v>12</v>
@@ -2710,13 +2720,13 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H70" t="s">
         <v>7</v>
@@ -2733,10 +2743,10 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C71" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H71" t="s">
         <v>7</v>
@@ -2748,7 +2758,7 @@
         <v>8</v>
       </c>
       <c r="K71" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L71" t="s">
         <v>12</v>
@@ -2771,10 +2781,7 @@
         <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>22</v>
-      </c>
-      <c r="K72" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L72" t="s">
         <v>23</v>
@@ -2797,10 +2804,7 @@
         <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>22</v>
-      </c>
-      <c r="K73" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L73" t="s">
         <v>23</v>
@@ -2823,10 +2827,7 @@
         <v>20</v>
       </c>
       <c r="J74" t="s">
-        <v>22</v>
-      </c>
-      <c r="K74" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L74" t="s">
         <v>23</v>
@@ -2834,7 +2835,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E75" t="s">
         <v>25</v>
@@ -2849,10 +2850,7 @@
         <v>10</v>
       </c>
       <c r="J75" t="s">
-        <v>22</v>
-      </c>
-      <c r="K75" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L75" t="s">
         <v>23</v>
@@ -2860,7 +2858,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E76" t="s">
         <v>26</v>
@@ -2875,10 +2873,7 @@
         <v>14</v>
       </c>
       <c r="J76" t="s">
-        <v>22</v>
-      </c>
-      <c r="K76" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L76" t="s">
         <v>23</v>
@@ -2886,7 +2881,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -2901,10 +2896,7 @@
         <v>25</v>
       </c>
       <c r="J77" t="s">
-        <v>22</v>
-      </c>
-      <c r="K77" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L77" t="s">
         <v>23</v>
@@ -2912,13 +2904,13 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C78" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -2933,10 +2925,7 @@
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>22</v>
-      </c>
-      <c r="K78" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L78" t="s">
         <v>23</v>
@@ -2944,10 +2933,10 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E79" t="s">
         <v>25</v>
@@ -2962,10 +2951,10 @@
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K79" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L79" t="s">
         <v>23</v>
@@ -2973,10 +2962,10 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E80" t="s">
         <v>26</v>
@@ -2991,10 +2980,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K80" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L80" t="s">
         <v>23</v>
@@ -3002,10 +2991,10 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C81" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3020,10 +3009,10 @@
         <v>35</v>
       </c>
       <c r="J81" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K81" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L81" t="s">
         <v>23</v>
@@ -3031,7 +3020,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3050,15 +3039,15 @@
         <v>4</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3077,15 +3066,15 @@
         <v>4</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3104,10 +3093,10 @@
         <v>20</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3121,16 +3110,13 @@
         <v>28</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I85">
         <v>3</v>
       </c>
       <c r="J85" t="s">
-        <v>22</v>
-      </c>
-      <c r="K85" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L85" t="s">
         <v>23</v>
@@ -3153,16 +3139,13 @@
         <v>28</v>
       </c>
       <c r="H86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I86">
         <v>18</v>
       </c>
       <c r="J86" t="s">
-        <v>22</v>
-      </c>
-      <c r="K86" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L86" t="s">
         <v>23</v>
@@ -3185,16 +3168,13 @@
         <v>28</v>
       </c>
       <c r="H87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I87">
         <v>17</v>
       </c>
       <c r="J87" t="s">
-        <v>22</v>
-      </c>
-      <c r="K87" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L87" t="s">
         <v>23</v>
@@ -3214,16 +3194,13 @@
         <v>28</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I88">
         <v>18</v>
       </c>
       <c r="J88" t="s">
-        <v>22</v>
-      </c>
-      <c r="K88" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L88" t="s">
         <v>23</v>
@@ -3243,16 +3220,13 @@
         <v>28</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I89">
         <v>18</v>
       </c>
       <c r="J89" t="s">
-        <v>22</v>
-      </c>
-      <c r="K89" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L89" t="s">
         <v>23</v>
@@ -3272,16 +3246,13 @@
         <v>28</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I90">
         <v>17</v>
       </c>
       <c r="J90" t="s">
-        <v>22</v>
-      </c>
-      <c r="K90" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L90" t="s">
         <v>23</v>
@@ -3301,16 +3272,13 @@
         <v>28</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I91">
         <v>17</v>
       </c>
       <c r="J91" t="s">
-        <v>22</v>
-      </c>
-      <c r="K91" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L91" t="s">
         <v>23</v>
@@ -3330,16 +3298,16 @@
         <v>28</v>
       </c>
       <c r="H92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I92">
         <v>17</v>
       </c>
       <c r="J92" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K92" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="L92" t="s">
         <v>23</v>
@@ -3356,16 +3324,13 @@
         <v>28</v>
       </c>
       <c r="H93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I93">
         <v>30</v>
       </c>
       <c r="J93" t="s">
-        <v>22</v>
-      </c>
-      <c r="K93" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L93" t="s">
         <v>23</v>
@@ -3373,7 +3338,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3386,21 +3351,21 @@
         <v>28</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I94" s="1">
         <v>3</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3413,21 +3378,21 @@
         <v>28</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I95" s="1">
         <v>17</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3440,21 +3405,21 @@
         <v>28</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I96" s="1">
         <v>30</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E97" t="s">
         <v>25</v>
@@ -3463,16 +3428,13 @@
         <v>28</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I97">
         <v>4</v>
       </c>
       <c r="J97" t="s">
-        <v>22</v>
-      </c>
-      <c r="K97" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L97" t="s">
         <v>23</v>
@@ -3480,7 +3442,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E98" t="s">
         <v>26</v>
@@ -3489,16 +3451,13 @@
         <v>28</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I98">
         <v>18</v>
       </c>
       <c r="J98" t="s">
-        <v>22</v>
-      </c>
-      <c r="K98" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L98" t="s">
         <v>23</v>
@@ -3506,7 +3465,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3515,16 +3474,13 @@
         <v>28</v>
       </c>
       <c r="H99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I99">
         <v>30</v>
       </c>
       <c r="J99" t="s">
-        <v>22</v>
-      </c>
-      <c r="K99" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L99" t="s">
         <v>23</v>
@@ -3532,13 +3488,13 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C100" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D100" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E100" t="s">
         <v>26</v>
@@ -3547,16 +3503,13 @@
         <v>28</v>
       </c>
       <c r="H100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I100">
         <v>5</v>
       </c>
       <c r="J100" t="s">
-        <v>22</v>
-      </c>
-      <c r="K100" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L100" t="s">
         <v>23</v>
@@ -3564,13 +3517,13 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C101" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D101" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3579,16 +3532,13 @@
         <v>28</v>
       </c>
       <c r="H101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I101">
         <v>5</v>
       </c>
       <c r="J101" t="s">
-        <v>22</v>
-      </c>
-      <c r="K101" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L101" t="s">
         <v>23</v>
@@ -3596,10 +3546,10 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C102" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E102" t="s">
         <v>25</v>
@@ -3608,16 +3558,16 @@
         <v>28</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I102">
         <v>4</v>
       </c>
       <c r="J102" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K102" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L102" t="s">
         <v>23</v>
@@ -3625,10 +3575,10 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C103" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E103" t="s">
         <v>26</v>
@@ -3637,16 +3587,16 @@
         <v>28</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I103">
         <v>12</v>
       </c>
       <c r="J103" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K103" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L103" t="s">
         <v>23</v>
@@ -3654,10 +3604,10 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C104" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3666,16 +3616,16 @@
         <v>28</v>
       </c>
       <c r="H104" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I104">
         <v>20</v>
       </c>
       <c r="J104" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K104" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L104" t="s">
         <v>23</v>
@@ -3686,19 +3636,16 @@
         <v>25</v>
       </c>
       <c r="G105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I105">
         <v>0.01</v>
       </c>
       <c r="J105" t="s">
-        <v>22</v>
-      </c>
-      <c r="K105" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="L105" t="s">
         <v>23</v>
@@ -3709,19 +3656,16 @@
         <v>26</v>
       </c>
       <c r="G106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I106">
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>22</v>
-      </c>
-      <c r="K106" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="L106" t="s">
         <v>23</v>
@@ -3732,19 +3676,16 @@
         <v>27</v>
       </c>
       <c r="G107" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I107">
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>22</v>
-      </c>
-      <c r="K107" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="L107" t="s">
         <v>23</v>
@@ -3755,19 +3696,16 @@
         <v>25</v>
       </c>
       <c r="G108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I108">
         <v>0.5</v>
       </c>
       <c r="J108" t="s">
-        <v>22</v>
-      </c>
-      <c r="K108" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L108" t="s">
         <v>23</v>
@@ -3778,19 +3716,16 @@
         <v>26</v>
       </c>
       <c r="G109" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I109">
         <v>0.5</v>
       </c>
       <c r="J109" t="s">
-        <v>22</v>
-      </c>
-      <c r="K109" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L109" t="s">
         <v>23</v>
@@ -3801,19 +3736,16 @@
         <v>27</v>
       </c>
       <c r="G110" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I110">
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>22</v>
-      </c>
-      <c r="K110" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L110" t="s">
         <v>23</v>
@@ -3824,19 +3756,16 @@
         <v>25</v>
       </c>
       <c r="G111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I111">
         <v>0.3</v>
       </c>
       <c r="J111" t="s">
-        <v>22</v>
-      </c>
-      <c r="K111" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="L111" t="s">
         <v>23</v>
@@ -3847,19 +3776,16 @@
         <v>26</v>
       </c>
       <c r="G112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I112">
         <v>30</v>
       </c>
       <c r="J112" t="s">
-        <v>22</v>
-      </c>
-      <c r="K112" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="L112" t="s">
         <v>23</v>
@@ -3870,19 +3796,16 @@
         <v>27</v>
       </c>
       <c r="G113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I113">
         <v>30</v>
       </c>
       <c r="J113" t="s">
-        <v>22</v>
-      </c>
-      <c r="K113" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="L113" t="s">
         <v>23</v>
@@ -3896,19 +3819,16 @@
         <v>25</v>
       </c>
       <c r="H114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I114">
         <v>60</v>
       </c>
       <c r="J114" t="s">
-        <v>22</v>
-      </c>
-      <c r="K114" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L114" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -3925,19 +3845,16 @@
         <v>26</v>
       </c>
       <c r="H115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I115">
         <v>51</v>
       </c>
       <c r="J115" t="s">
-        <v>22</v>
-      </c>
-      <c r="K115" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L115" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -3954,19 +3871,16 @@
         <v>26</v>
       </c>
       <c r="H116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I116">
         <v>52</v>
       </c>
       <c r="J116" t="s">
-        <v>22</v>
-      </c>
-      <c r="K116" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L116" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -3980,19 +3894,16 @@
         <v>26</v>
       </c>
       <c r="H117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I117">
         <v>51</v>
       </c>
       <c r="J117" t="s">
-        <v>22</v>
-      </c>
-      <c r="K117" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L117" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -4006,19 +3917,16 @@
         <v>26</v>
       </c>
       <c r="H118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I118">
         <v>51</v>
       </c>
       <c r="J118" t="s">
-        <v>22</v>
-      </c>
-      <c r="K118" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L118" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -4032,19 +3940,16 @@
         <v>26</v>
       </c>
       <c r="H119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I119">
         <v>52</v>
       </c>
       <c r="J119" t="s">
-        <v>22</v>
-      </c>
-      <c r="K119" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L119" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -4058,19 +3963,16 @@
         <v>26</v>
       </c>
       <c r="H120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I120">
         <v>52</v>
       </c>
       <c r="J120" t="s">
-        <v>22</v>
-      </c>
-      <c r="K120" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L120" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -4084,16 +3986,16 @@
         <v>26</v>
       </c>
       <c r="H121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I121">
         <v>52</v>
       </c>
       <c r="J121" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K121" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -4104,342 +4006,349 @@
         <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I122">
         <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>22</v>
-      </c>
-      <c r="K122" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="L122" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
+        <v>1</v>
+      </c>
       <c r="E123" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I123" s="1">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1" t="s">
+      <c r="A124" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I124" s="5">
+        <v>24</v>
+      </c>
+      <c r="J124" t="s">
+        <v>79</v>
+      </c>
+      <c r="K124" s="1"/>
+      <c r="L124" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="5"/>
+      <c r="E125" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I124" s="1">
-        <v>52</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1" t="s">
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I125" s="5">
+        <v>25</v>
+      </c>
+      <c r="J125" t="s">
+        <v>79</v>
+      </c>
+      <c r="K125" s="1"/>
+      <c r="L125" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I125" s="1">
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I126" s="5">
         <v>10</v>
       </c>
-      <c r="J125" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>68</v>
-      </c>
-      <c r="C126" t="s">
-        <v>69</v>
-      </c>
-      <c r="H126" t="s">
-        <v>35</v>
-      </c>
-      <c r="I126">
-        <v>40</v>
-      </c>
       <c r="J126" t="s">
-        <v>22</v>
-      </c>
-      <c r="K126" t="s">
-        <v>30</v>
+        <v>79</v>
+      </c>
+      <c r="K126" s="1"/>
+      <c r="L126" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>45</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="A127" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" s="1">
         <v>25</v>
       </c>
-      <c r="H127" t="s">
-        <v>35</v>
-      </c>
-      <c r="I127">
-        <v>70</v>
-      </c>
-      <c r="J127" t="s">
-        <v>22</v>
-      </c>
-      <c r="K127" t="s">
-        <v>30</v>
+      <c r="J127" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>45</v>
-      </c>
-      <c r="E128" t="s">
+        <v>65</v>
+      </c>
+      <c r="C128" t="s">
+        <v>66</v>
+      </c>
+      <c r="H128" t="s">
+        <v>34</v>
+      </c>
+      <c r="I128">
+        <v>40</v>
+      </c>
+      <c r="J128" t="s">
+        <v>79</v>
+      </c>
+      <c r="L128" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I129" s="1">
+        <v>0</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>44</v>
+      </c>
+      <c r="E130" t="s">
+        <v>25</v>
+      </c>
+      <c r="H130" t="s">
+        <v>34</v>
+      </c>
+      <c r="I130">
+        <v>70</v>
+      </c>
+      <c r="J130" t="s">
+        <v>79</v>
+      </c>
+      <c r="L130" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>44</v>
+      </c>
+      <c r="E131" t="s">
         <v>26</v>
       </c>
-      <c r="H128" t="s">
-        <v>35</v>
-      </c>
-      <c r="I128">
+      <c r="H131" t="s">
+        <v>34</v>
+      </c>
+      <c r="I131">
         <v>51</v>
       </c>
-      <c r="J128" t="s">
-        <v>22</v>
-      </c>
-      <c r="K128" t="s">
+      <c r="J131" t="s">
+        <v>79</v>
+      </c>
+      <c r="L131" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>44</v>
+      </c>
+      <c r="E132" t="s">
+        <v>27</v>
+      </c>
+      <c r="H132" t="s">
+        <v>34</v>
+      </c>
+      <c r="I132">
+        <v>10</v>
+      </c>
+      <c r="J132" t="s">
+        <v>79</v>
+      </c>
+      <c r="L132" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H134" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I134" s="1">
+        <v>0</v>
+      </c>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H135" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>45</v>
-      </c>
-      <c r="E129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H129" t="s">
-        <v>35</v>
-      </c>
-      <c r="I129">
-        <v>10</v>
-      </c>
-      <c r="J129" t="s">
-        <v>22</v>
-      </c>
-      <c r="K129" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H131" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I131" s="1">
+      <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H132" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I132" s="1">
+      <c r="J135" s="1"/>
+      <c r="K135" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H136" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="1"/>
-      <c r="K132" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H133" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I133" s="1">
-        <v>0</v>
-      </c>
-      <c r="J133" s="1"/>
-      <c r="K133" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B135" s="3"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3"/>
-      <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
-      <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
-      <c r="I135" s="3"/>
-      <c r="J135" s="3"/>
-      <c r="K135" s="3"/>
-      <c r="L135" s="3"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>1</v>
-      </c>
-      <c r="C136" t="s">
-        <v>2</v>
-      </c>
-      <c r="D136" t="s">
-        <v>3</v>
-      </c>
-      <c r="H136" t="s">
-        <v>4</v>
-      </c>
-      <c r="I136">
-        <v>5.39</v>
-      </c>
-      <c r="J136" t="s">
-        <v>5</v>
-      </c>
-      <c r="L136" t="s">
-        <v>6</v>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>1</v>
-      </c>
-      <c r="C137" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137" t="s">
-        <v>3</v>
-      </c>
-      <c r="H137" t="s">
-        <v>4</v>
-      </c>
-      <c r="I137">
-        <v>2.8</v>
-      </c>
-      <c r="J137" t="s">
-        <v>5</v>
-      </c>
-      <c r="K137" t="s">
-        <v>10</v>
-      </c>
-      <c r="L137" t="s">
-        <v>11</v>
-      </c>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>1</v>
-      </c>
-      <c r="D138" t="s">
-        <v>13</v>
-      </c>
-      <c r="H138" t="s">
-        <v>4</v>
-      </c>
-      <c r="I138">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J138" t="s">
-        <v>5</v>
-      </c>
-      <c r="L138" t="s">
-        <v>11</v>
-      </c>
+      <c r="A138" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="3"/>
+      <c r="K138" s="3"/>
+      <c r="L138" s="3"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
+      <c r="C139" t="s">
+        <v>2</v>
+      </c>
       <c r="D139" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H139" t="s">
         <v>4</v>
       </c>
       <c r="I139">
-        <v>0.79</v>
+        <v>5.39</v>
       </c>
       <c r="J139" t="s">
         <v>5</v>
       </c>
-      <c r="K139" t="s">
-        <v>15</v>
-      </c>
       <c r="L139" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1</v>
       </c>
+      <c r="C140" t="s">
+        <v>9</v>
+      </c>
       <c r="D140" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H140" t="s">
         <v>4</v>
       </c>
       <c r="I140">
-        <v>2.2599999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="J140" t="s">
         <v>5</v>
       </c>
+      <c r="K140" t="s">
+        <v>10</v>
+      </c>
       <c r="L140" t="s">
         <v>11</v>
       </c>
@@ -4449,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H141" t="s">
         <v>4</v>
@@ -4469,18 +4378,81 @@
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H142" t="s">
         <v>4</v>
       </c>
       <c r="I142">
-        <v>2.2599999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="J142" t="s">
         <v>5</v>
       </c>
       <c r="K142" t="s">
+        <v>15</v>
+      </c>
+      <c r="L142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1</v>
+      </c>
+      <c r="D143" t="s">
+        <v>17</v>
+      </c>
+      <c r="H143" t="s">
+        <v>4</v>
+      </c>
+      <c r="I143">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J143" t="s">
+        <v>5</v>
+      </c>
+      <c r="L143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1</v>
+      </c>
+      <c r="D144" t="s">
+        <v>16</v>
+      </c>
+      <c r="H144" t="s">
+        <v>4</v>
+      </c>
+      <c r="I144">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J144" t="s">
+        <v>5</v>
+      </c>
+      <c r="L144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1</v>
+      </c>
+      <c r="D145" t="s">
+        <v>18</v>
+      </c>
+      <c r="H145" t="s">
+        <v>4</v>
+      </c>
+      <c r="I145">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J145" t="s">
+        <v>5</v>
+      </c>
+      <c r="K145" t="s">
         <v>19</v>
       </c>
     </row>

--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -267,7 +267,7 @@
     <t>% of TAN</t>
   </si>
   <si>
-    <t>Assume same as solid manure</t>
+    <t>Table 3.9. EMEP/EEA air pollutant emission inventory Guidebook 2019</t>
   </si>
 </sst>
 </file>
@@ -4022,21 +4022,22 @@
       <c r="A123" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E123" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1" t="s">
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I123" s="1">
-        <v>52</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K123" s="1" t="s">
+      <c r="I123" s="5">
+        <v>60</v>
+      </c>
+      <c r="J123" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K123" s="1"/>
+      <c r="L123" t="s">
         <v>82</v>
       </c>
     </row>
@@ -4119,27 +4120,28 @@
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
-      <c r="E127" s="1" t="s">
+      <c r="E127" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1" t="s">
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I127" s="1">
-        <v>25</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K127" s="1" t="s">
+      <c r="I127" s="5">
+        <v>60</v>
+      </c>
+      <c r="J127" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K127" s="1"/>
+      <c r="L127" t="s">
         <v>82</v>
       </c>
     </row>

--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="93">
   <si>
     <t>value</t>
   </si>
@@ -51,9 +51,6 @@
     <t>beef</t>
   </si>
   <si>
-    <t>Avg stable and grazing period accounting for 5.1 month stable period</t>
-  </si>
-  <si>
     <t>NIR 2022 Table 5.16</t>
   </si>
   <si>
@@ -268,13 +265,46 @@
   </si>
   <si>
     <t>Table 3.9. EMEP/EEA air pollutant emission inventory Guidebook 2019</t>
+  </si>
+  <si>
+    <t>Assume same as sows</t>
+  </si>
+  <si>
+    <t>methane_B0</t>
+  </si>
+  <si>
+    <t>m3 CH4/kg VS</t>
+  </si>
+  <si>
+    <t>Fallback</t>
+  </si>
+  <si>
+    <t>kg CH4/animal/yr</t>
+  </si>
+  <si>
+    <t>methane_per_head</t>
+  </si>
+  <si>
+    <t>sheep</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>methane_MCF</t>
+  </si>
+  <si>
+    <t>% of B0</t>
+  </si>
+  <si>
+    <t>NIR 2022 Table 5.18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,6 +450,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -772,13 +809,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1100,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1108,7 +1147,7 @@
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" customWidth="1"/>
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="63.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="68.140625" bestFit="1" customWidth="1"/>
@@ -1116,45 +1155,45 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1179,19 +1218,19 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1205,19 +1244,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4">
         <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1225,22 +1264,22 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I5">
         <v>49</v>
       </c>
       <c r="J5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1248,22 +1287,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <v>30</v>
       </c>
       <c r="J6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1271,25 +1310,25 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1297,25 +1336,25 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8">
         <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1323,22 +1362,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
         <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1352,19 +1391,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10">
         <v>66</v>
       </c>
       <c r="J10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,19 +1417,19 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11">
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1398,22 +1437,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1421,22 +1460,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13">
         <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1444,25 +1483,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I14">
         <v>36</v>
       </c>
       <c r="J14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1470,25 +1509,25 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I15">
         <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1496,22 +1535,22 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16">
         <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1525,19 +1564,19 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I17">
         <v>8</v>
       </c>
       <c r="J17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1551,19 +1590,19 @@
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18">
         <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1571,22 +1610,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19">
         <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1594,22 +1633,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20">
         <v>14</v>
       </c>
       <c r="J20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1617,25 +1656,25 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21">
         <v>17</v>
       </c>
       <c r="J21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1643,25 +1682,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I22">
         <v>17</v>
       </c>
       <c r="J22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1669,22 +1708,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23">
         <v>17</v>
       </c>
       <c r="J23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1698,19 +1737,19 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1724,19 +1763,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I25">
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1744,22 +1783,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26">
         <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1767,22 +1806,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27">
         <v>37</v>
       </c>
       <c r="J27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1790,25 +1829,25 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28">
         <v>27</v>
       </c>
       <c r="J28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1816,25 +1855,25 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29">
         <v>27</v>
       </c>
       <c r="J29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -1842,571 +1881,571 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I30">
         <v>27</v>
       </c>
       <c r="J30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I31" s="1">
         <f>100-I32-I33-I34</f>
         <v>65</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I33">
         <v>33</v>
       </c>
       <c r="J33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I34">
         <v>2</v>
       </c>
       <c r="J34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I37">
         <v>61</v>
       </c>
       <c r="J37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
         <v>44</v>
       </c>
-      <c r="D38" t="s">
-        <v>45</v>
-      </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I38">
         <v>97</v>
       </c>
       <c r="J38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I39">
         <v>97</v>
       </c>
       <c r="J39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I40">
         <v>19</v>
       </c>
       <c r="J40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
         <v>44</v>
       </c>
-      <c r="D41" t="s">
-        <v>45</v>
-      </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I41">
         <v>2</v>
       </c>
       <c r="J41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I42">
         <v>2</v>
       </c>
       <c r="J42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I43">
         <v>20</v>
       </c>
       <c r="J43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
         <v>44</v>
       </c>
-      <c r="D44" t="s">
-        <v>45</v>
-      </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I44">
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" t="s">
         <v>46</v>
       </c>
-      <c r="E45" t="s">
-        <v>27</v>
-      </c>
-      <c r="H45" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" t="s">
-        <v>47</v>
-      </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" t="s">
         <v>65</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>66</v>
       </c>
-      <c r="D46" t="s">
-        <v>67</v>
-      </c>
       <c r="E46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" t="s">
         <v>65</v>
       </c>
-      <c r="C47" t="s">
-        <v>66</v>
-      </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" t="s">
         <v>65</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>66</v>
       </c>
-      <c r="D48" t="s">
-        <v>67</v>
-      </c>
       <c r="E48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" t="s">
         <v>65</v>
       </c>
-      <c r="C49" t="s">
-        <v>66</v>
-      </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I49">
         <v>9</v>
       </c>
       <c r="J49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" t="s">
         <v>65</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>66</v>
       </c>
-      <c r="D50" t="s">
-        <v>67</v>
-      </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
         <v>65</v>
       </c>
-      <c r="C51" t="s">
-        <v>66</v>
-      </c>
       <c r="E51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I51">
         <v>86</v>
       </c>
       <c r="J51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
         <v>65</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>66</v>
       </c>
-      <c r="D52" t="s">
-        <v>67</v>
-      </c>
       <c r="E52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I52">
         <v>100</v>
       </c>
       <c r="J52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" t="s">
         <v>65</v>
       </c>
-      <c r="C53" t="s">
-        <v>66</v>
-      </c>
       <c r="E53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I53">
         <v>5</v>
       </c>
       <c r="J53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2463,7 +2502,7 @@
         <v>8</v>
       </c>
       <c r="L57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -2471,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H58" t="s">
         <v>7</v>
@@ -2483,7 +2522,7 @@
         <v>8</v>
       </c>
       <c r="L58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2491,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59" t="s">
         <v>7</v>
@@ -2503,7 +2542,7 @@
         <v>8</v>
       </c>
       <c r="L59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -2511,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H60" t="s">
         <v>7</v>
@@ -2523,7 +2562,7 @@
         <v>8</v>
       </c>
       <c r="L60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2531,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
         <v>7</v>
@@ -2543,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="L61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2551,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
         <v>7</v>
@@ -2563,15 +2602,15 @@
         <v>8</v>
       </c>
       <c r="K62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H63" t="s">
         <v>7</v>
@@ -2583,15 +2622,15 @@
         <v>8</v>
       </c>
       <c r="L63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H64" t="s">
         <v>7</v>
@@ -2603,15 +2642,15 @@
         <v>8</v>
       </c>
       <c r="L64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H65" t="s">
         <v>7</v>
@@ -2623,15 +2662,15 @@
         <v>8</v>
       </c>
       <c r="L65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H66" t="s">
         <v>7</v>
@@ -2643,18 +2682,18 @@
         <v>8</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H67" t="s">
         <v>7</v>
@@ -2666,18 +2705,18 @@
         <v>8</v>
       </c>
       <c r="K67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" t="s">
         <v>44</v>
-      </c>
-      <c r="D68" t="s">
-        <v>45</v>
       </c>
       <c r="H68" t="s">
         <v>7</v>
@@ -2689,18 +2728,18 @@
         <v>8</v>
       </c>
       <c r="K68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H69" t="s">
         <v>7</v>
@@ -2712,21 +2751,21 @@
         <v>8</v>
       </c>
       <c r="K69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="C70" t="s">
         <v>65</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>66</v>
-      </c>
-      <c r="D70" t="s">
-        <v>67</v>
       </c>
       <c r="H70" t="s">
         <v>7</v>
@@ -2738,15 +2777,15 @@
         <v>8</v>
       </c>
       <c r="L70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" t="s">
         <v>65</v>
-      </c>
-      <c r="C71" t="s">
-        <v>66</v>
       </c>
       <c r="H71" t="s">
         <v>7</v>
@@ -2758,10 +2797,10 @@
         <v>8</v>
       </c>
       <c r="K71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -2769,22 +2808,22 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G72" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" t="s">
         <v>28</v>
-      </c>
-      <c r="H72" t="s">
-        <v>29</v>
       </c>
       <c r="I72">
         <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L72" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -2792,22 +2831,22 @@
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G73" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" t="s">
         <v>28</v>
-      </c>
-      <c r="H73" t="s">
-        <v>29</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -2815,288 +2854,288 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" t="s">
         <v>27</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>28</v>
       </c>
-      <c r="H74" t="s">
-        <v>29</v>
-      </c>
       <c r="I74">
         <v>20</v>
       </c>
       <c r="J74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G75" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" t="s">
         <v>28</v>
-      </c>
-      <c r="H75" t="s">
-        <v>29</v>
       </c>
       <c r="I75">
         <v>10</v>
       </c>
       <c r="J75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" t="s">
         <v>28</v>
-      </c>
-      <c r="H76" t="s">
-        <v>29</v>
       </c>
       <c r="I76">
         <v>14</v>
       </c>
       <c r="J76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E77" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" t="s">
         <v>27</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>28</v>
-      </c>
-      <c r="H77" t="s">
-        <v>29</v>
       </c>
       <c r="I77">
         <v>25</v>
       </c>
       <c r="J77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" t="s">
         <v>65</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>66</v>
       </c>
-      <c r="D78" t="s">
-        <v>67</v>
-      </c>
       <c r="E78" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" t="s">
         <v>27</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>28</v>
-      </c>
-      <c r="H78" t="s">
-        <v>29</v>
       </c>
       <c r="I78">
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" t="s">
         <v>65</v>
       </c>
-      <c r="C79" t="s">
-        <v>66</v>
-      </c>
       <c r="E79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G79" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" t="s">
         <v>28</v>
-      </c>
-      <c r="H79" t="s">
-        <v>29</v>
       </c>
       <c r="I79">
         <v>10</v>
       </c>
       <c r="J79" t="s">
+        <v>78</v>
+      </c>
+      <c r="K79" t="s">
         <v>79</v>
       </c>
-      <c r="K79" t="s">
-        <v>80</v>
-      </c>
       <c r="L79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" t="s">
         <v>65</v>
       </c>
-      <c r="C80" t="s">
-        <v>66</v>
-      </c>
       <c r="E80" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G80" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" t="s">
         <v>28</v>
-      </c>
-      <c r="H80" t="s">
-        <v>29</v>
       </c>
       <c r="I80">
         <v>10</v>
       </c>
       <c r="J80" t="s">
+        <v>78</v>
+      </c>
+      <c r="K80" t="s">
         <v>79</v>
       </c>
-      <c r="K80" t="s">
-        <v>80</v>
-      </c>
       <c r="L80" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" t="s">
         <v>65</v>
       </c>
-      <c r="C81" t="s">
-        <v>66</v>
-      </c>
       <c r="E81" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" t="s">
         <v>27</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>28</v>
-      </c>
-      <c r="H81" t="s">
-        <v>29</v>
       </c>
       <c r="I81">
         <v>35</v>
       </c>
       <c r="J81" t="s">
+        <v>78</v>
+      </c>
+      <c r="K81" t="s">
         <v>79</v>
       </c>
-      <c r="K81" t="s">
-        <v>80</v>
-      </c>
       <c r="L81" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="I82" s="1">
         <v>4</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H83" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="I83" s="1">
         <v>4</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="I84" s="1">
         <v>20</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3104,22 +3143,22 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I85">
         <v>3</v>
       </c>
       <c r="J85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -3133,22 +3172,22 @@
         <v>3</v>
       </c>
       <c r="E86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I86">
         <v>18</v>
       </c>
       <c r="J86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -3162,22 +3201,22 @@
         <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I87">
         <v>17</v>
       </c>
       <c r="J87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -3185,25 +3224,25 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I88">
         <v>18</v>
       </c>
       <c r="J88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -3211,25 +3250,25 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I89">
         <v>18</v>
       </c>
       <c r="J89" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -3237,25 +3276,25 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I90">
         <v>17</v>
       </c>
       <c r="J90" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L90" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -3263,25 +3302,25 @@
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I91">
         <v>17</v>
       </c>
       <c r="J91" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -3289,28 +3328,28 @@
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I92">
         <v>17</v>
       </c>
       <c r="J92" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -3318,497 +3357,497 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" t="s">
         <v>27</v>
       </c>
-      <c r="G93" t="s">
-        <v>28</v>
-      </c>
       <c r="H93" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I93">
         <v>30</v>
       </c>
       <c r="J93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L93" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I94" s="1">
         <v>3</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I95" s="1">
         <v>17</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I96" s="1">
         <v>30</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I97">
         <v>4</v>
       </c>
       <c r="J97" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L97" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E98" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I98">
         <v>18</v>
       </c>
       <c r="J98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E99" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" t="s">
         <v>27</v>
       </c>
-      <c r="G99" t="s">
-        <v>28</v>
-      </c>
       <c r="H99" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I99">
         <v>30</v>
       </c>
       <c r="J99" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>64</v>
+      </c>
+      <c r="C100" t="s">
         <v>65</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>66</v>
       </c>
-      <c r="D100" t="s">
-        <v>67</v>
-      </c>
       <c r="E100" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H100" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I100">
         <v>5</v>
       </c>
       <c r="J100" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>64</v>
+      </c>
+      <c r="C101" t="s">
         <v>65</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>66</v>
       </c>
-      <c r="D101" t="s">
-        <v>67</v>
-      </c>
       <c r="E101" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" t="s">
         <v>27</v>
       </c>
-      <c r="G101" t="s">
-        <v>28</v>
-      </c>
       <c r="H101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I101">
         <v>5</v>
       </c>
       <c r="J101" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L101" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>64</v>
+      </c>
+      <c r="C102" t="s">
         <v>65</v>
       </c>
-      <c r="C102" t="s">
-        <v>66</v>
-      </c>
       <c r="E102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G102" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I102">
         <v>4</v>
       </c>
       <c r="J102" t="s">
+        <v>78</v>
+      </c>
+      <c r="K102" t="s">
         <v>79</v>
       </c>
-      <c r="K102" t="s">
-        <v>80</v>
-      </c>
       <c r="L102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>64</v>
+      </c>
+      <c r="C103" t="s">
         <v>65</v>
       </c>
-      <c r="C103" t="s">
-        <v>66</v>
-      </c>
       <c r="E103" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I103">
         <v>12</v>
       </c>
       <c r="J103" t="s">
+        <v>78</v>
+      </c>
+      <c r="K103" t="s">
         <v>79</v>
       </c>
-      <c r="K103" t="s">
-        <v>80</v>
-      </c>
       <c r="L103" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>64</v>
+      </c>
+      <c r="C104" t="s">
         <v>65</v>
       </c>
-      <c r="C104" t="s">
-        <v>66</v>
-      </c>
       <c r="E104" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" t="s">
         <v>27</v>
       </c>
-      <c r="G104" t="s">
-        <v>28</v>
-      </c>
       <c r="H104" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I104">
         <v>20</v>
       </c>
       <c r="J104" t="s">
+        <v>78</v>
+      </c>
+      <c r="K104" t="s">
         <v>79</v>
       </c>
-      <c r="K104" t="s">
-        <v>80</v>
-      </c>
       <c r="L104" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I105">
         <v>0.01</v>
       </c>
       <c r="J105" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I106">
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E107" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H107" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I107">
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H108" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I108">
         <v>0.5</v>
       </c>
       <c r="J108" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L108" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E109" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I109">
         <v>0.5</v>
       </c>
       <c r="J109" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L109" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E110" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I110">
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L110" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H111" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I111">
         <v>0.3</v>
       </c>
       <c r="J111" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E112" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I112">
         <v>30</v>
       </c>
       <c r="J112" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L112" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I113">
         <v>30</v>
       </c>
       <c r="J113" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L113" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -3816,19 +3855,19 @@
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I114">
         <v>60</v>
       </c>
       <c r="J114" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L114" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -3842,19 +3881,19 @@
         <v>3</v>
       </c>
       <c r="E115" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I115">
         <v>51</v>
       </c>
       <c r="J115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L115" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -3868,19 +3907,19 @@
         <v>3</v>
       </c>
       <c r="E116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I116">
         <v>52</v>
       </c>
       <c r="J116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L116" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -3888,22 +3927,22 @@
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I117">
         <v>51</v>
       </c>
       <c r="J117" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L117" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -3911,22 +3950,22 @@
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H118" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I118">
         <v>51</v>
       </c>
       <c r="J118" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L118" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -3934,22 +3973,22 @@
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E119" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H119" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I119">
         <v>52</v>
       </c>
       <c r="J119" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L119" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -3957,22 +3996,22 @@
         <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E120" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H120" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I120">
         <v>52</v>
       </c>
       <c r="J120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L120" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -3980,22 +4019,22 @@
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H121" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I121">
         <v>52</v>
       </c>
       <c r="J121" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K121" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -4003,19 +4042,19 @@
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I122">
         <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L122" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -4023,151 +4062,151 @@
         <v>1</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I123" s="5">
         <v>60</v>
       </c>
       <c r="J123" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K123" s="1"/>
       <c r="L123" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
       <c r="H124" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I124" s="5">
         <v>24</v>
       </c>
       <c r="J124" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K124" s="1"/>
       <c r="L124" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I125" s="5">
         <v>25</v>
       </c>
       <c r="J125" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K125" s="1"/>
       <c r="L125" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I126" s="5">
         <v>10</v>
       </c>
       <c r="J126" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K126" s="1"/>
       <c r="L126" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
       <c r="H127" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I127" s="5">
         <v>60</v>
       </c>
       <c r="J127" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K127" s="1"/>
       <c r="L127" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>64</v>
+      </c>
+      <c r="C128" t="s">
         <v>65</v>
       </c>
-      <c r="C128" t="s">
-        <v>66</v>
-      </c>
       <c r="H128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I128">
         <v>40</v>
       </c>
       <c r="J128" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L128" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4176,112 +4215,112 @@
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
       <c r="H129" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I129" s="1">
         <v>0</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E130" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H130" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I130">
         <v>70</v>
       </c>
       <c r="J130" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L130" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I131">
         <v>51</v>
       </c>
       <c r="J131" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L131" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E132" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H132" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I132">
         <v>10</v>
       </c>
       <c r="J132" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L132" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H134" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="1"/>
       <c r="K134" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H135" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H136" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="1"/>
       <c r="K136" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -4292,7 +4331,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -4307,26 +4346,17 @@
       <c r="L138" s="3"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>1</v>
-      </c>
-      <c r="C139" t="s">
-        <v>2</v>
-      </c>
-      <c r="D139" t="s">
-        <v>3</v>
-      </c>
-      <c r="H139" t="s">
+      <c r="H139" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I139">
-        <v>5.39</v>
-      </c>
-      <c r="J139" t="s">
+      <c r="I139" s="7">
+        <v>0</v>
+      </c>
+      <c r="J139" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="L139" t="s">
-        <v>6</v>
+      <c r="K139" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -4334,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="C140" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D140" t="s">
         <v>3</v>
@@ -4343,59 +4373,62 @@
         <v>4</v>
       </c>
       <c r="I140">
-        <v>2.8</v>
+        <v>5.39</v>
       </c>
       <c r="J140" t="s">
         <v>5</v>
       </c>
-      <c r="K140" t="s">
-        <v>10</v>
-      </c>
       <c r="L140" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1</v>
       </c>
+      <c r="C141" t="s">
+        <v>9</v>
+      </c>
       <c r="D141" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H141" t="s">
         <v>4</v>
       </c>
-      <c r="I141">
-        <v>2.2599999999999998</v>
+      <c r="I141" s="6">
+        <v>2.2999999999999998</v>
       </c>
       <c r="J141" t="s">
         <v>5</v>
       </c>
       <c r="L141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1</v>
       </c>
+      <c r="C142" t="s">
+        <v>9</v>
+      </c>
       <c r="D142" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="E142" t="s">
+        <v>19</v>
       </c>
       <c r="H142" t="s">
         <v>4</v>
       </c>
-      <c r="I142">
-        <v>0.79</v>
+      <c r="I142" s="6">
+        <v>3.17</v>
       </c>
       <c r="J142" t="s">
         <v>5</v>
       </c>
-      <c r="K142" t="s">
-        <v>15</v>
-      </c>
       <c r="L142" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -4403,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="D143" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H143" t="s">
         <v>4</v>
@@ -4415,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="L143" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -4423,27 +4456,30 @@
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H144" t="s">
         <v>4</v>
       </c>
       <c r="I144">
-        <v>2.2599999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="J144" t="s">
         <v>5</v>
       </c>
+      <c r="K144" t="s">
+        <v>14</v>
+      </c>
       <c r="L144" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1</v>
       </c>
       <c r="D145" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H145" t="s">
         <v>4</v>
@@ -4454,8 +4490,401 @@
       <c r="J145" t="s">
         <v>5</v>
       </c>
-      <c r="K145" t="s">
+      <c r="L145" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1</v>
+      </c>
+      <c r="D146" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" t="s">
+        <v>4</v>
+      </c>
+      <c r="I146">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J146" t="s">
+        <v>5</v>
+      </c>
+      <c r="L146" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
+        <v>17</v>
+      </c>
+      <c r="H147" t="s">
+        <v>4</v>
+      </c>
+      <c r="I147">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J147" t="s">
+        <v>5</v>
+      </c>
+      <c r="K147" t="s">
+        <v>18</v>
+      </c>
+      <c r="L147" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>43</v>
+      </c>
+      <c r="D148" t="s">
+        <v>50</v>
+      </c>
+      <c r="H148" t="s">
+        <v>4</v>
+      </c>
+      <c r="I148">
+        <v>0.69</v>
+      </c>
+      <c r="J148" t="s">
+        <v>5</v>
+      </c>
+      <c r="L148" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>43</v>
+      </c>
+      <c r="D149" t="s">
+        <v>51</v>
+      </c>
+      <c r="H149" t="s">
+        <v>4</v>
+      </c>
+      <c r="I149">
+        <v>0.45</v>
+      </c>
+      <c r="J149" t="s">
+        <v>5</v>
+      </c>
+      <c r="L149" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>43</v>
+      </c>
+      <c r="D150" t="s">
+        <v>52</v>
+      </c>
+      <c r="H150" t="s">
+        <v>4</v>
+      </c>
+      <c r="I150">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="J150" t="s">
+        <v>5</v>
+      </c>
+      <c r="L150" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>43</v>
+      </c>
+      <c r="D151" t="s">
+        <v>53</v>
+      </c>
+      <c r="H151" t="s">
+        <v>4</v>
+      </c>
+      <c r="I151">
+        <v>0.69</v>
+      </c>
+      <c r="J151" t="s">
+        <v>5</v>
+      </c>
+      <c r="K151" t="s">
+        <v>82</v>
+      </c>
+      <c r="L151" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>43</v>
+      </c>
+      <c r="D152" t="s">
+        <v>44</v>
+      </c>
+      <c r="H152" t="s">
+        <v>4</v>
+      </c>
+      <c r="I152">
+        <v>0.37</v>
+      </c>
+      <c r="J152" t="s">
+        <v>5</v>
+      </c>
+      <c r="L152" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>43</v>
+      </c>
+      <c r="D153" t="s">
+        <v>45</v>
+      </c>
+      <c r="H153" t="s">
+        <v>4</v>
+      </c>
+      <c r="I153">
+        <v>0.37</v>
+      </c>
+      <c r="J153" t="s">
+        <v>5</v>
+      </c>
+      <c r="L153" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H155" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I155" s="7">
+        <v>0</v>
+      </c>
+      <c r="J155" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K155" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1</v>
+      </c>
+      <c r="C156" t="s">
+        <v>2</v>
+      </c>
+      <c r="D156" t="s">
+        <v>3</v>
+      </c>
+      <c r="H156" t="s">
+        <v>83</v>
+      </c>
+      <c r="I156">
+        <v>0.24</v>
+      </c>
+      <c r="J156" t="s">
+        <v>84</v>
+      </c>
+      <c r="L156" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>83</v>
+      </c>
+      <c r="I157">
+        <v>0.18</v>
+      </c>
+      <c r="J157" t="s">
+        <v>84</v>
+      </c>
+      <c r="L157" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>43</v>
+      </c>
+      <c r="H158" t="s">
+        <v>83</v>
+      </c>
+      <c r="I158">
+        <v>0.45</v>
+      </c>
+      <c r="J158" t="s">
+        <v>84</v>
+      </c>
+      <c r="L158" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H160" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I160" s="7">
+        <v>0</v>
+      </c>
+      <c r="J160" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>69</v>
+      </c>
+      <c r="H161" t="s">
+        <v>87</v>
+      </c>
+      <c r="I161">
+        <v>1.56</v>
+      </c>
+      <c r="J161" t="s">
+        <v>86</v>
+      </c>
+      <c r="L161" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>88</v>
+      </c>
+      <c r="H162" t="s">
+        <v>87</v>
+      </c>
+      <c r="I162">
+        <v>0.19</v>
+      </c>
+      <c r="J162" t="s">
+        <v>86</v>
+      </c>
+      <c r="L162" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>64</v>
+      </c>
+      <c r="C163" t="s">
+        <v>65</v>
+      </c>
+      <c r="H163" t="s">
+        <v>87</v>
+      </c>
+      <c r="I163">
+        <v>0.02</v>
+      </c>
+      <c r="J163" t="s">
+        <v>86</v>
+      </c>
+      <c r="L163" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>64</v>
+      </c>
+      <c r="C164" t="s">
+        <v>89</v>
+      </c>
+      <c r="H164" t="s">
+        <v>87</v>
+      </c>
+      <c r="I164">
+        <v>0.03</v>
+      </c>
+      <c r="J164" t="s">
+        <v>86</v>
+      </c>
+      <c r="L164" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E166" s="5" t="s">
         <v>19</v>
+      </c>
+      <c r="H166" t="s">
+        <v>90</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166" t="s">
+        <v>91</v>
+      </c>
+      <c r="L166" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E167" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H167" t="s">
+        <v>90</v>
+      </c>
+      <c r="I167">
+        <v>3.5</v>
+      </c>
+      <c r="J167" t="s">
+        <v>91</v>
+      </c>
+      <c r="L167" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E168" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H168" t="s">
+        <v>90</v>
+      </c>
+      <c r="I168">
+        <v>2</v>
+      </c>
+      <c r="J168" t="s">
+        <v>91</v>
+      </c>
+      <c r="L168" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E169" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H169" t="s">
+        <v>90</v>
+      </c>
+      <c r="I169">
+        <v>17</v>
+      </c>
+      <c r="J169" t="s">
+        <v>91</v>
+      </c>
+      <c r="L169" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="92">
   <si>
     <t>value</t>
   </si>
@@ -231,18 +231,6 @@
     <t>horses</t>
   </si>
   <si>
-    <t>NIR 2022 Table 5.10</t>
-  </si>
-  <si>
-    <t>NIR 2022 Table 5.11</t>
-  </si>
-  <si>
-    <t>NIR 2022 Table 5.12</t>
-  </si>
-  <si>
-    <t>Remaining is grazing??</t>
-  </si>
-  <si>
     <t>Same as cattle??</t>
   </si>
   <si>
@@ -252,9 +240,6 @@
     <t>Swedish IIR 2019 Table 5-10</t>
   </si>
   <si>
-    <t>mammadjuren</t>
-  </si>
-  <si>
     <t>% of total N</t>
   </si>
   <si>
@@ -298,6 +283,18 @@
   </si>
   <si>
     <t>NIR 2022 Table 5.18</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023 Table 5-4</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023 Table 5-5</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023 Table 5-6</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2023 Table 5-7</t>
   </si>
 </sst>
 </file>
@@ -1139,21 +1136,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L169"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="63.140625" customWidth="1"/>
     <col min="12" max="12" width="68.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -1191,7 +1188,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -1207,7 +1204,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1224,16 +1221,20 @@
         <v>20</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="M3">
+        <f>I3+I16+I31+I46</f>
+        <v>95.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1250,16 +1251,20 @@
         <v>20</v>
       </c>
       <c r="I4">
-        <v>51</v>
+        <v>57.4</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M15" si="0">I4+I17+I32+I47</f>
+        <v>98.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1273,16 +1278,20 @@
         <v>20</v>
       </c>
       <c r="I5">
-        <v>49</v>
+        <v>52.7</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1296,16 +1305,20 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="J6" t="s">
         <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1319,7 +1332,7 @@
         <v>20</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>23.9</v>
       </c>
       <c r="J7" t="s">
         <v>21</v>
@@ -1328,10 +1341,14 @@
         <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>96.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -1345,7 +1362,7 @@
         <v>20</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>23.9</v>
       </c>
       <c r="J8" t="s">
         <v>21</v>
@@ -1354,10 +1371,14 @@
         <v>23</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>96.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -1371,7 +1392,7 @@
         <v>20</v>
       </c>
       <c r="I9">
-        <v>21</v>
+        <v>23.9</v>
       </c>
       <c r="J9" t="s">
         <v>21</v>
@@ -1379,163 +1400,186 @@
       <c r="K9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="L9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>96.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="5">
+        <v>50</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5">
+        <v>50</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="0"/>
+        <v>81.099999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>81.099999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>100.00000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D16" t="s">
         <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10">
-        <v>66</v>
-      </c>
-      <c r="J10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11">
-        <v>11</v>
-      </c>
-      <c r="J11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12">
-        <v>26</v>
-      </c>
-      <c r="J12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13">
-        <v>19</v>
-      </c>
-      <c r="J13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14">
-        <v>36</v>
-      </c>
-      <c r="J14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15">
-        <v>36</v>
-      </c>
-      <c r="J15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>17</v>
       </c>
       <c r="E16" t="s">
         <v>24</v>
@@ -1544,13 +1588,13 @@
         <v>20</v>
       </c>
       <c r="I16">
-        <v>36</v>
+        <v>63.7</v>
       </c>
       <c r="J16" t="s">
         <v>21</v>
       </c>
-      <c r="K16" t="s">
-        <v>18</v>
+      <c r="L16" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1558,51 +1602,48 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" t="s">
         <v>20</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="J17" t="s">
         <v>21</v>
       </c>
       <c r="L17" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
       <c r="D18" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" t="s">
         <v>20</v>
       </c>
       <c r="I18">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J18" t="s">
         <v>21</v>
       </c>
       <c r="L18" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1610,22 +1651,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s">
         <v>20</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>16.8</v>
       </c>
       <c r="J19" t="s">
         <v>21</v>
       </c>
       <c r="L19" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1633,22 +1674,25 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" t="s">
         <v>20</v>
       </c>
       <c r="I20">
-        <v>14</v>
+        <v>36.5</v>
       </c>
       <c r="J20" t="s">
         <v>21</v>
       </c>
+      <c r="K20" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="L20" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1656,16 +1700,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" t="s">
         <v>20</v>
       </c>
       <c r="I21">
-        <v>17</v>
+        <v>36.5</v>
       </c>
       <c r="J21" t="s">
         <v>21</v>
@@ -1674,7 +1718,7 @@
         <v>23</v>
       </c>
       <c r="L21" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,272 +1726,275 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22" t="s">
         <v>20</v>
       </c>
       <c r="I22">
-        <v>17</v>
+        <v>36.5</v>
       </c>
       <c r="J22" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>23</v>
+      <c r="K22" t="s">
+        <v>18</v>
       </c>
       <c r="L22" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H23" t="s">
         <v>20</v>
       </c>
       <c r="I23">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J23" t="s">
         <v>21</v>
       </c>
-      <c r="K23" t="s">
-        <v>18</v>
+      <c r="L23" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H24" t="s">
         <v>20</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="s">
         <v>21</v>
       </c>
       <c r="L24" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H25" t="s">
         <v>20</v>
       </c>
       <c r="I25">
-        <v>23</v>
+        <v>45.4</v>
       </c>
       <c r="J25" t="s">
         <v>21</v>
       </c>
+      <c r="K25" t="s">
+        <v>47</v>
+      </c>
       <c r="L25" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H26" t="s">
         <v>20</v>
       </c>
       <c r="I26">
-        <v>15</v>
+        <v>77.8</v>
       </c>
       <c r="J26" t="s">
         <v>21</v>
       </c>
+      <c r="K26" t="s">
+        <v>46</v>
+      </c>
       <c r="L26" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H27" t="s">
         <v>20</v>
       </c>
       <c r="I27">
-        <v>37</v>
+        <v>77.8</v>
       </c>
       <c r="J27" t="s">
         <v>21</v>
       </c>
+      <c r="K27" t="s">
+        <v>46</v>
+      </c>
       <c r="L27" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>15</v>
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H28" t="s">
         <v>20</v>
       </c>
       <c r="I28">
-        <v>27</v>
+        <v>6.9</v>
       </c>
       <c r="J28" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="L28" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H29" t="s">
         <v>20</v>
       </c>
       <c r="I29">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J29" t="s">
         <v>21</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="L29" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" t="s">
-        <v>17</v>
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H30" t="s">
         <v>20</v>
       </c>
       <c r="I30">
-        <v>27</v>
+        <v>6.9</v>
       </c>
       <c r="J30" t="s">
         <v>21</v>
       </c>
       <c r="K30" t="s">
-        <v>18</v>
+        <v>68</v>
+      </c>
+      <c r="L30" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="1">
-        <f>100-I32-I33-I34</f>
-        <v>65</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>73</v>
+      <c r="A31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J31" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s">
         <v>20</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="J32" t="s">
         <v>21</v>
       </c>
       <c r="L32" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
@@ -1956,160 +2003,154 @@
         <v>20</v>
       </c>
       <c r="I33">
-        <v>33</v>
+        <v>7.9</v>
       </c>
       <c r="J33" t="s">
         <v>21</v>
       </c>
       <c r="L33" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s">
         <v>20</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>11.9</v>
       </c>
       <c r="J34" t="s">
         <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H35" t="s">
         <v>20</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="J35" t="s">
         <v>21</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" t="s">
-        <v>59</v>
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H36" t="s">
         <v>20</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="J36" t="s">
         <v>21</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="L36" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H37" t="s">
         <v>20</v>
       </c>
       <c r="I37">
-        <v>61</v>
+        <v>10.6</v>
       </c>
       <c r="J37" t="s">
         <v>21</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="L37" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H38" t="s">
         <v>20</v>
       </c>
       <c r="I38">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="J38" t="s">
         <v>21</v>
       </c>
-      <c r="K38" t="s">
-        <v>46</v>
-      </c>
       <c r="L38" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s">
         <v>20</v>
       </c>
       <c r="I39">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="J39" t="s">
         <v>21</v>
       </c>
-      <c r="K39" t="s">
-        <v>46</v>
-      </c>
       <c r="L39" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2123,7 +2164,7 @@
         <v>20</v>
       </c>
       <c r="I40">
-        <v>19</v>
+        <v>23.8</v>
       </c>
       <c r="J40" t="s">
         <v>21</v>
@@ -2132,7 +2173,7 @@
         <v>47</v>
       </c>
       <c r="L40" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2149,7 +2190,7 @@
         <v>20</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J41" t="s">
         <v>21</v>
@@ -2158,7 +2199,7 @@
         <v>46</v>
       </c>
       <c r="L41" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2175,7 +2216,7 @@
         <v>20</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J42" t="s">
         <v>21</v>
@@ -2184,228 +2225,240 @@
         <v>46</v>
       </c>
       <c r="L42" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>84</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H43" t="s">
         <v>20</v>
       </c>
       <c r="I43">
-        <v>20</v>
+        <v>89.9</v>
       </c>
       <c r="J43" t="s">
         <v>21</v>
       </c>
-      <c r="K43" t="s">
-        <v>47</v>
-      </c>
       <c r="L43" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>65</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H44" t="s">
         <v>20</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="s">
         <v>21</v>
       </c>
-      <c r="K44" t="s">
-        <v>46</v>
-      </c>
       <c r="L44" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" t="s">
-        <v>45</v>
+        <v>64</v>
+      </c>
+      <c r="C45" t="s">
+        <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H45" t="s">
         <v>20</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>89.9</v>
       </c>
       <c r="J45" t="s">
         <v>21</v>
       </c>
       <c r="K45" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="L45" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H46" t="s">
         <v>20</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="s">
         <v>21</v>
+      </c>
+      <c r="L46" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H47" t="s">
         <v>20</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="J47" t="s">
         <v>21</v>
+      </c>
+      <c r="L47" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H48" t="s">
         <v>20</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="J48" t="s">
         <v>21</v>
+      </c>
+      <c r="L48" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C49" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H49" t="s">
         <v>20</v>
       </c>
       <c r="I49">
-        <v>9</v>
+        <v>33.5</v>
       </c>
       <c r="J49" t="s">
         <v>21</v>
       </c>
-      <c r="K49" t="s">
-        <v>68</v>
+      <c r="L49" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H50" t="s">
         <v>20</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="J50" t="s">
         <v>21</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H51" t="s">
         <v>20</v>
       </c>
       <c r="I51">
-        <v>86</v>
+        <v>25.6</v>
       </c>
       <c r="J51" t="s">
         <v>21</v>
       </c>
-      <c r="K51" t="s">
-        <v>68</v>
+      <c r="K51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E52" t="s">
         <v>26</v>
@@ -2414,18 +2467,21 @@
         <v>20</v>
       </c>
       <c r="I52">
-        <v>100</v>
+        <v>25.6</v>
       </c>
       <c r="J52" t="s">
         <v>21</v>
+      </c>
+      <c r="K52" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E53" t="s">
         <v>26</v>
@@ -2434,209 +2490,239 @@
         <v>20</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="s">
         <v>21</v>
       </c>
-      <c r="K53" t="s">
-        <v>68</v>
+      <c r="L53" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" t="s">
+        <v>26</v>
+      </c>
+      <c r="H54" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
+      <c r="A55" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55">
+        <v>19.8</v>
+      </c>
+      <c r="J55" t="s">
+        <v>21</v>
+      </c>
+      <c r="K55" t="s">
+        <v>47</v>
+      </c>
+      <c r="L55" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D56" t="s">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="E56" t="s">
+        <v>26</v>
       </c>
       <c r="H56" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I56">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="K56" t="s">
+        <v>46</v>
       </c>
       <c r="L56" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D57" t="s">
-        <v>3</v>
+        <v>45</v>
+      </c>
+      <c r="E57" t="s">
+        <v>26</v>
       </c>
       <c r="H57" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I57">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="K57" t="s">
+        <v>46</v>
       </c>
       <c r="L57" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="C58" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" t="s">
+        <v>26</v>
       </c>
       <c r="H58" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I58">
-        <v>47</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L58" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="C59" t="s">
+        <v>65</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>66</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
       </c>
       <c r="H59" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I59">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="J59" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L59" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" t="s">
-        <v>15</v>
+        <v>64</v>
+      </c>
+      <c r="C60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" t="s">
+        <v>26</v>
       </c>
       <c r="H60" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I60">
-        <v>47</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="K60" t="s">
+        <v>68</v>
       </c>
       <c r="L60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" t="s">
-        <v>7</v>
-      </c>
-      <c r="I61">
-        <v>47</v>
-      </c>
-      <c r="J61" t="s">
-        <v>8</v>
-      </c>
-      <c r="L61" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" t="s">
-        <v>17</v>
-      </c>
-      <c r="H62" t="s">
-        <v>7</v>
-      </c>
-      <c r="I62">
-        <v>47</v>
-      </c>
-      <c r="J62" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" t="s">
-        <v>18</v>
-      </c>
-      <c r="L62" t="s">
-        <v>11</v>
-      </c>
+      <c r="A62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>3</v>
       </c>
       <c r="H63" t="s">
         <v>7</v>
       </c>
       <c r="I63">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="J63" t="s">
         <v>8</v>
       </c>
       <c r="L63" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H64" t="s">
         <v>7</v>
       </c>
       <c r="I64">
-        <v>22.5</v>
+        <v>63</v>
       </c>
       <c r="J64" t="s">
         <v>8</v>
@@ -2647,16 +2733,16 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="H65" t="s">
         <v>7</v>
       </c>
       <c r="I65">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="J65" t="s">
         <v>8</v>
@@ -2667,91 +2753,82 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="H66" t="s">
         <v>7</v>
       </c>
       <c r="I66">
-        <v>1.2</v>
+        <v>28</v>
       </c>
       <c r="J66" t="s">
         <v>8</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="L66" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="H67" t="s">
         <v>7</v>
       </c>
       <c r="I67">
-        <v>9.5</v>
+        <v>47</v>
       </c>
       <c r="J67" t="s">
         <v>8</v>
       </c>
-      <c r="K67" t="s">
-        <v>54</v>
-      </c>
       <c r="L67" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H68" t="s">
         <v>7</v>
       </c>
       <c r="I68">
-        <v>9.5</v>
+        <v>47</v>
       </c>
       <c r="J68" t="s">
         <v>8</v>
       </c>
-      <c r="K68" t="s">
-        <v>55</v>
-      </c>
       <c r="L68" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
         <v>7</v>
       </c>
       <c r="I69">
-        <v>9.5</v>
+        <v>47</v>
       </c>
       <c r="J69" t="s">
         <v>8</v>
       </c>
       <c r="K69" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="L69" t="s">
         <v>11</v>
@@ -2759,19 +2836,13 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="C70" t="s">
-        <v>65</v>
-      </c>
-      <c r="D70" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H70" t="s">
         <v>7</v>
       </c>
       <c r="I70">
-        <v>0.28999999999999998</v>
+        <v>48</v>
       </c>
       <c r="J70" t="s">
         <v>8</v>
@@ -2782,163 +2853,154 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>64</v>
-      </c>
-      <c r="C71" t="s">
-        <v>65</v>
+        <v>43</v>
+      </c>
+      <c r="D71" t="s">
+        <v>50</v>
       </c>
       <c r="H71" t="s">
         <v>7</v>
       </c>
       <c r="I71">
-        <v>0.6</v>
+        <v>22.5</v>
       </c>
       <c r="J71" t="s">
         <v>8</v>
       </c>
-      <c r="K71" t="s">
-        <v>67</v>
-      </c>
       <c r="L71" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>24</v>
-      </c>
-      <c r="G72" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="D72" t="s">
+        <v>51</v>
       </c>
       <c r="H72" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J72" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="L72" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
-        <v>25</v>
-      </c>
-      <c r="G73" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="D73" t="s">
+        <v>52</v>
       </c>
       <c r="H73" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="s">
-        <v>78</v>
+        <v>8</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="L73" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="D74" t="s">
+        <v>53</v>
       </c>
       <c r="H74" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I74">
-        <v>20</v>
+        <v>9.5</v>
       </c>
       <c r="J74" t="s">
-        <v>78</v>
+        <v>8</v>
+      </c>
+      <c r="K74" t="s">
+        <v>54</v>
       </c>
       <c r="L74" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>43</v>
       </c>
-      <c r="E75" t="s">
-        <v>24</v>
-      </c>
-      <c r="G75" t="s">
-        <v>27</v>
+      <c r="D75" t="s">
+        <v>44</v>
       </c>
       <c r="H75" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I75">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J75" t="s">
-        <v>78</v>
+        <v>8</v>
+      </c>
+      <c r="K75" t="s">
+        <v>55</v>
       </c>
       <c r="L75" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>43</v>
       </c>
-      <c r="E76" t="s">
-        <v>25</v>
-      </c>
-      <c r="G76" t="s">
-        <v>27</v>
+      <c r="D76" t="s">
+        <v>45</v>
       </c>
       <c r="H76" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I76">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="J76" t="s">
-        <v>78</v>
+        <v>8</v>
+      </c>
+      <c r="K76" t="s">
+        <v>55</v>
       </c>
       <c r="L76" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>43</v>
-      </c>
-      <c r="E77" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" t="s">
-        <v>27</v>
+        <v>64</v>
+      </c>
+      <c r="C77" t="s">
+        <v>84</v>
       </c>
       <c r="H77" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I77">
-        <v>25</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="L77" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -2951,23 +3013,17 @@
       <c r="D78" t="s">
         <v>66</v>
       </c>
-      <c r="E78" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" t="s">
-        <v>27</v>
-      </c>
       <c r="H78" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I78">
-        <v>10</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J78" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="L78" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -2977,37 +3033,28 @@
       <c r="C79" t="s">
         <v>65</v>
       </c>
-      <c r="E79" t="s">
-        <v>24</v>
-      </c>
-      <c r="G79" t="s">
-        <v>27</v>
-      </c>
       <c r="H79" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I79">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="K79" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="L79" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>64</v>
-      </c>
-      <c r="C80" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G80" t="s">
         <v>27</v>
@@ -3016,13 +3063,10 @@
         <v>28</v>
       </c>
       <c r="I80">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J80" t="s">
-        <v>78</v>
-      </c>
-      <c r="K80" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L80" t="s">
         <v>22</v>
@@ -3030,13 +3074,10 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>64</v>
-      </c>
-      <c r="C81" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G81" t="s">
         <v>27</v>
@@ -3045,117 +3086,102 @@
         <v>28</v>
       </c>
       <c r="I81">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J81" t="s">
-        <v>78</v>
-      </c>
-      <c r="K81" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L81" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1" t="s">
+      <c r="A82" t="s">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s">
+        <v>73</v>
+      </c>
+      <c r="L82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>43</v>
+      </c>
+      <c r="E83" t="s">
         <v>24</v>
       </c>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1" t="s">
+      <c r="G83" t="s">
         <v>27</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H83" t="s">
         <v>28</v>
       </c>
-      <c r="I82" s="1">
-        <v>4</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1" t="s">
+      <c r="I83">
+        <v>10</v>
+      </c>
+      <c r="J83" t="s">
+        <v>73</v>
+      </c>
+      <c r="L83" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>43</v>
+      </c>
+      <c r="E84" t="s">
         <v>25</v>
       </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1" t="s">
+      <c r="G84" t="s">
         <v>27</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H84" t="s">
         <v>28</v>
       </c>
-      <c r="I83" s="1">
-        <v>4</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I84" s="1">
-        <v>20</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>74</v>
+      <c r="I84">
+        <v>14</v>
+      </c>
+      <c r="J84" t="s">
+        <v>73</v>
+      </c>
+      <c r="L84" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="E85" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G85" t="s">
         <v>27</v>
       </c>
       <c r="H85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J85" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L85" t="s">
         <v>22</v>
@@ -3163,28 +3189,25 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C86" t="s">
-        <v>2</v>
-      </c>
-      <c r="D86" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="E86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G86" t="s">
         <v>27</v>
       </c>
       <c r="H86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I86">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J86" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L86" t="s">
         <v>22</v>
@@ -3192,13 +3215,10 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>9</v>
-      </c>
-      <c r="D87" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
@@ -3207,13 +3227,13 @@
         <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I87">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J87" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L87" t="s">
         <v>22</v>
@@ -3221,25 +3241,25 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="C88" t="s">
+        <v>84</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G88" t="s">
         <v>27</v>
       </c>
       <c r="H88" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I88">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J88" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L88" t="s">
         <v>22</v>
@@ -3247,25 +3267,28 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="C89" t="s">
+        <v>65</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="E89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G89" t="s">
         <v>27</v>
       </c>
       <c r="H89" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I89">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L89" t="s">
         <v>22</v>
@@ -3273,25 +3296,28 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" t="s">
-        <v>15</v>
+        <v>64</v>
+      </c>
+      <c r="C90" t="s">
+        <v>65</v>
       </c>
       <c r="E90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G90" t="s">
         <v>27</v>
       </c>
       <c r="H90" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I90">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J90" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="K90" t="s">
+        <v>74</v>
       </c>
       <c r="L90" t="s">
         <v>22</v>
@@ -3299,10 +3325,10 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" t="s">
-        <v>16</v>
+        <v>64</v>
+      </c>
+      <c r="C91" t="s">
+        <v>65</v>
       </c>
       <c r="E91" t="s">
         <v>25</v>
@@ -3311,13 +3337,16 @@
         <v>27</v>
       </c>
       <c r="H91" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I91">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J91" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="K91" t="s">
+        <v>74</v>
       </c>
       <c r="L91" t="s">
         <v>22</v>
@@ -3325,54 +3354,58 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" t="s">
-        <v>17</v>
+        <v>64</v>
+      </c>
+      <c r="C92" t="s">
+        <v>65</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G92" t="s">
         <v>27</v>
       </c>
       <c r="H92" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I92">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="J92" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K92" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="L92" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>1</v>
-      </c>
-      <c r="E93" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" t="s">
+      <c r="A93" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H93" t="s">
-        <v>29</v>
-      </c>
-      <c r="I93">
-        <v>30</v>
-      </c>
-      <c r="J93" t="s">
-        <v>78</v>
-      </c>
-      <c r="L93" t="s">
-        <v>22</v>
+      <c r="H93" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I93" s="1">
+        <v>4</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -3383,23 +3416,23 @@
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I94" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -3410,58 +3443,60 @@
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H95" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="1">
+        <v>20</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" t="s">
         <v>29</v>
       </c>
-      <c r="I95" s="1">
-        <v>17</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I96" s="1">
-        <v>30</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>74</v>
+      <c r="I96">
+        <v>3</v>
+      </c>
+      <c r="J96" t="s">
+        <v>73</v>
+      </c>
+      <c r="L96" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" t="s">
+        <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G97" t="s">
         <v>27</v>
@@ -3470,10 +3505,10 @@
         <v>29</v>
       </c>
       <c r="I97">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L97" t="s">
         <v>22</v>
@@ -3481,7 +3516,13 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" t="s">
+        <v>3</v>
       </c>
       <c r="E98" t="s">
         <v>25</v>
@@ -3493,10 +3534,10 @@
         <v>29</v>
       </c>
       <c r="I98">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J98" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L98" t="s">
         <v>22</v>
@@ -3504,10 +3545,13 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G99" t="s">
         <v>27</v>
@@ -3516,10 +3560,10 @@
         <v>29</v>
       </c>
       <c r="I99">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J99" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L99" t="s">
         <v>22</v>
@@ -3527,13 +3571,10 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>64</v>
-      </c>
-      <c r="C100" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="E100" t="s">
         <v>25</v>
@@ -3545,10 +3586,10 @@
         <v>29</v>
       </c>
       <c r="I100">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L100" t="s">
         <v>22</v>
@@ -3556,16 +3597,13 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>64</v>
-      </c>
-      <c r="C101" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="E101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G101" t="s">
         <v>27</v>
@@ -3574,10 +3612,10 @@
         <v>29</v>
       </c>
       <c r="I101">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J101" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L101" t="s">
         <v>22</v>
@@ -3585,13 +3623,13 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>64</v>
-      </c>
-      <c r="C102" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="D102" t="s">
+        <v>16</v>
       </c>
       <c r="E102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G102" t="s">
         <v>27</v>
@@ -3600,13 +3638,10 @@
         <v>29</v>
       </c>
       <c r="I102">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J102" t="s">
-        <v>78</v>
-      </c>
-      <c r="K102" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L102" t="s">
         <v>22</v>
@@ -3614,10 +3649,10 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>64</v>
-      </c>
-      <c r="C103" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="D103" t="s">
+        <v>17</v>
       </c>
       <c r="E103" t="s">
         <v>25</v>
@@ -3629,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="I103">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J103" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K103" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="L103" t="s">
         <v>22</v>
@@ -3643,10 +3678,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>64</v>
-      </c>
-      <c r="C104" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="E104" t="s">
         <v>26</v>
@@ -3658,193 +3690,238 @@
         <v>29</v>
       </c>
       <c r="I104">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J104" t="s">
-        <v>78</v>
-      </c>
-      <c r="K104" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L104" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E105" t="s">
+      <c r="A105" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G105" t="s">
+      <c r="F105" s="1"/>
+      <c r="G105" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I105" s="1">
+        <v>3</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I106" s="1">
+        <v>17</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I107" s="1">
         <v>30</v>
       </c>
-      <c r="H105" t="s">
-        <v>29</v>
-      </c>
-      <c r="I105">
-        <v>0.01</v>
-      </c>
-      <c r="J105" t="s">
-        <v>80</v>
-      </c>
-      <c r="L105" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E106" t="s">
-        <v>25</v>
-      </c>
-      <c r="G106" t="s">
-        <v>30</v>
-      </c>
-      <c r="H106" t="s">
-        <v>29</v>
-      </c>
-      <c r="I106">
-        <v>1</v>
-      </c>
-      <c r="J106" t="s">
-        <v>80</v>
-      </c>
-      <c r="L106" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E107" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" t="s">
-        <v>30</v>
-      </c>
-      <c r="H107" t="s">
-        <v>29</v>
-      </c>
-      <c r="I107">
-        <v>1</v>
-      </c>
-      <c r="J107" t="s">
-        <v>80</v>
-      </c>
-      <c r="L107" t="s">
-        <v>22</v>
+      <c r="J107" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>43</v>
+      </c>
       <c r="E108" t="s">
         <v>24</v>
       </c>
       <c r="G108" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H108" t="s">
         <v>29</v>
       </c>
       <c r="I108">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J108" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L108" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>43</v>
+      </c>
       <c r="E109" t="s">
         <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H109" t="s">
         <v>29</v>
       </c>
       <c r="I109">
-        <v>0.5</v>
+        <v>18</v>
       </c>
       <c r="J109" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L109" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>43</v>
+      </c>
       <c r="E110" t="s">
         <v>26</v>
       </c>
       <c r="G110" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H110" t="s">
         <v>29</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J110" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L110" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" t="s">
+        <v>84</v>
+      </c>
       <c r="E111" t="s">
         <v>24</v>
       </c>
       <c r="G111" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H111" t="s">
         <v>29</v>
       </c>
       <c r="I111">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J111" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L111" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>64</v>
+      </c>
+      <c r="C112" t="s">
+        <v>84</v>
+      </c>
       <c r="E112" t="s">
         <v>25</v>
       </c>
       <c r="G112" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H112" t="s">
         <v>29</v>
       </c>
       <c r="I112">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J112" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L112" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>64</v>
+      </c>
+      <c r="C113" t="s">
+        <v>84</v>
+      </c>
       <c r="E113" t="s">
         <v>26</v>
       </c>
       <c r="G113" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H113" t="s">
         <v>29</v>
       </c>
       <c r="I113">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J113" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L113" t="s">
         <v>22</v>
@@ -3852,404 +3929,407 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="C114" t="s">
+        <v>65</v>
+      </c>
+      <c r="D114" t="s">
+        <v>66</v>
       </c>
       <c r="E114" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G114" t="s">
+        <v>27</v>
       </c>
       <c r="H114" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I114">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="J114" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L114" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C115" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D115" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="E115" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G115" t="s">
+        <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I115">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="J115" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L115" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C116" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="E116" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="G116" t="s">
+        <v>27</v>
       </c>
       <c r="H116" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I116">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="J116" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="K116" t="s">
+        <v>74</v>
       </c>
       <c r="L116" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1</v>
-      </c>
-      <c r="D117" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="C117" t="s">
+        <v>65</v>
       </c>
       <c r="E117" t="s">
         <v>25</v>
       </c>
+      <c r="G117" t="s">
+        <v>27</v>
+      </c>
       <c r="H117" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I117">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="J117" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="K117" t="s">
+        <v>74</v>
       </c>
       <c r="L117" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1</v>
-      </c>
-      <c r="D118" t="s">
-        <v>13</v>
+        <v>64</v>
+      </c>
+      <c r="C118" t="s">
+        <v>65</v>
       </c>
       <c r="E118" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G118" t="s">
+        <v>27</v>
       </c>
       <c r="H118" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I118">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="J118" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="K118" t="s">
+        <v>74</v>
       </c>
       <c r="L118" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>1</v>
-      </c>
-      <c r="D119" t="s">
-        <v>15</v>
-      </c>
       <c r="E119" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="G119" t="s">
+        <v>30</v>
       </c>
       <c r="H119" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I119">
-        <v>52</v>
+        <v>0.01</v>
       </c>
       <c r="J119" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L119" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>1</v>
-      </c>
-      <c r="D120" t="s">
-        <v>16</v>
-      </c>
       <c r="E120" t="s">
         <v>25</v>
       </c>
+      <c r="G120" t="s">
+        <v>30</v>
+      </c>
       <c r="H120" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I120">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L120" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>1</v>
-      </c>
-      <c r="D121" t="s">
-        <v>17</v>
-      </c>
       <c r="E121" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" t="s">
+        <v>30</v>
+      </c>
+      <c r="H121" t="s">
+        <v>29</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121" t="s">
+        <v>75</v>
+      </c>
+      <c r="L121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E122" t="s">
+        <v>24</v>
+      </c>
+      <c r="G122" t="s">
+        <v>31</v>
+      </c>
+      <c r="H122" t="s">
+        <v>29</v>
+      </c>
+      <c r="I122">
+        <v>0.5</v>
+      </c>
+      <c r="J122" t="s">
+        <v>73</v>
+      </c>
+      <c r="L122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E123" t="s">
         <v>25</v>
       </c>
-      <c r="H121" t="s">
-        <v>33</v>
-      </c>
-      <c r="I121">
-        <v>52</v>
-      </c>
-      <c r="J121" t="s">
-        <v>78</v>
-      </c>
-      <c r="K121" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>1</v>
-      </c>
-      <c r="E122" t="s">
+      <c r="G123" t="s">
+        <v>31</v>
+      </c>
+      <c r="H123" t="s">
+        <v>29</v>
+      </c>
+      <c r="I123">
+        <v>0.5</v>
+      </c>
+      <c r="J123" t="s">
+        <v>73</v>
+      </c>
+      <c r="L123" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E124" t="s">
         <v>26</v>
       </c>
-      <c r="H122" t="s">
-        <v>33</v>
-      </c>
-      <c r="I122">
-        <v>10</v>
-      </c>
-      <c r="J122" t="s">
-        <v>78</v>
-      </c>
-      <c r="L122" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F123" s="5"/>
-      <c r="G123" s="5"/>
-      <c r="H123" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I123" s="5">
-        <v>60</v>
-      </c>
-      <c r="J123" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K123" s="1"/>
-      <c r="L123" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5" t="s">
+      <c r="G124" t="s">
+        <v>31</v>
+      </c>
+      <c r="H124" t="s">
+        <v>29</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124" t="s">
+        <v>73</v>
+      </c>
+      <c r="L124" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E125" t="s">
         <v>24</v>
       </c>
-      <c r="F124" s="5"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I124" s="5">
-        <v>24</v>
-      </c>
-      <c r="J124" t="s">
-        <v>78</v>
-      </c>
-      <c r="K124" s="1"/>
-      <c r="L124" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B125" s="5"/>
-      <c r="C125" s="5"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="5" t="s">
+      <c r="G125" t="s">
+        <v>32</v>
+      </c>
+      <c r="H125" t="s">
+        <v>29</v>
+      </c>
+      <c r="I125">
+        <v>0.3</v>
+      </c>
+      <c r="J125" t="s">
+        <v>75</v>
+      </c>
+      <c r="L125" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E126" t="s">
         <v>25</v>
       </c>
-      <c r="F125" s="5"/>
-      <c r="G125" s="5"/>
-      <c r="H125" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I125" s="5">
-        <v>25</v>
-      </c>
-      <c r="J125" t="s">
-        <v>78</v>
-      </c>
-      <c r="K125" s="1"/>
-      <c r="L125" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5" t="s">
+      <c r="G126" t="s">
+        <v>32</v>
+      </c>
+      <c r="H126" t="s">
+        <v>29</v>
+      </c>
+      <c r="I126">
+        <v>30</v>
+      </c>
+      <c r="J126" t="s">
+        <v>75</v>
+      </c>
+      <c r="L126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E127" t="s">
         <v>26</v>
       </c>
-      <c r="F126" s="5"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I126" s="5">
-        <v>10</v>
-      </c>
-      <c r="J126" t="s">
-        <v>78</v>
-      </c>
-      <c r="K126" s="1"/>
-      <c r="L126" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I127" s="5">
-        <v>60</v>
-      </c>
-      <c r="J127" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K127" s="1"/>
+      <c r="G127" t="s">
+        <v>32</v>
+      </c>
+      <c r="H127" t="s">
+        <v>29</v>
+      </c>
+      <c r="I127">
+        <v>30</v>
+      </c>
+      <c r="J127" t="s">
+        <v>75</v>
+      </c>
       <c r="L127" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>64</v>
-      </c>
-      <c r="C128" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="E128" t="s">
+        <v>24</v>
       </c>
       <c r="H128" t="s">
         <v>33</v>
       </c>
       <c r="I128">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J128" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L128" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
-      <c r="G129" s="1"/>
-      <c r="H129" s="1" t="s">
+      <c r="A129" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E129" t="s">
+        <v>25</v>
+      </c>
+      <c r="H129" t="s">
         <v>33</v>
       </c>
-      <c r="I129" s="1">
-        <v>0</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>77</v>
+      <c r="I129">
+        <v>51</v>
+      </c>
+      <c r="J129" t="s">
+        <v>73</v>
+      </c>
+      <c r="L129" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" t="s">
+        <v>3</v>
       </c>
       <c r="E130" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H130" t="s">
         <v>33</v>
       </c>
       <c r="I130">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="J130" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L130" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="D131" t="s">
+        <v>12</v>
       </c>
       <c r="E131" t="s">
         <v>25</v>
@@ -4261,630 +4341,1082 @@
         <v>51</v>
       </c>
       <c r="J131" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L131" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
       </c>
       <c r="E132" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H132" t="s">
         <v>33</v>
       </c>
       <c r="I132">
+        <v>51</v>
+      </c>
+      <c r="J132" t="s">
+        <v>73</v>
+      </c>
+      <c r="L132" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1</v>
+      </c>
+      <c r="D133" t="s">
+        <v>15</v>
+      </c>
+      <c r="E133" t="s">
+        <v>25</v>
+      </c>
+      <c r="H133" t="s">
+        <v>33</v>
+      </c>
+      <c r="I133">
+        <v>52</v>
+      </c>
+      <c r="J133" t="s">
+        <v>73</v>
+      </c>
+      <c r="L133" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" t="s">
+        <v>25</v>
+      </c>
+      <c r="H134" t="s">
+        <v>33</v>
+      </c>
+      <c r="I134">
+        <v>52</v>
+      </c>
+      <c r="J134" t="s">
+        <v>73</v>
+      </c>
+      <c r="L134" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135" t="s">
+        <v>25</v>
+      </c>
+      <c r="H135" t="s">
+        <v>33</v>
+      </c>
+      <c r="I135">
+        <v>52</v>
+      </c>
+      <c r="J135" t="s">
+        <v>73</v>
+      </c>
+      <c r="K135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1</v>
+      </c>
+      <c r="E136" t="s">
+        <v>26</v>
+      </c>
+      <c r="H136" t="s">
+        <v>33</v>
+      </c>
+      <c r="I136">
         <v>10</v>
       </c>
-      <c r="J132" t="s">
-        <v>78</v>
-      </c>
-      <c r="L132" t="s">
+      <c r="J136" t="s">
+        <v>73</v>
+      </c>
+      <c r="L136" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I137" s="5">
+        <v>60</v>
+      </c>
+      <c r="J137" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K137" s="1"/>
+      <c r="L137" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H134" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I134" s="1">
-        <v>0</v>
-      </c>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H135" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I135" s="1">
-        <v>0</v>
-      </c>
-      <c r="J135" s="1"/>
-      <c r="K135" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H136" s="1" t="s">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I136" s="1">
-        <v>0</v>
-      </c>
-      <c r="J136" s="1"/>
-      <c r="K136" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B138" s="3"/>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
-      <c r="H138" s="3"/>
-      <c r="I138" s="3"/>
-      <c r="J138" s="3"/>
-      <c r="K138" s="3"/>
-      <c r="L138" s="3"/>
+      <c r="I138" s="5">
+        <v>24</v>
+      </c>
+      <c r="J138" t="s">
+        <v>73</v>
+      </c>
+      <c r="K138" s="1"/>
+      <c r="L138" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H139" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I139" s="7">
-        <v>0</v>
-      </c>
-      <c r="J139" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="K139" s="7" t="s">
-        <v>85</v>
+      <c r="A139" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I139" s="5">
+        <v>25</v>
+      </c>
+      <c r="J139" t="s">
+        <v>73</v>
+      </c>
+      <c r="K139" s="1"/>
+      <c r="L139" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>1</v>
-      </c>
-      <c r="C140" t="s">
-        <v>2</v>
-      </c>
-      <c r="D140" t="s">
-        <v>3</v>
-      </c>
-      <c r="H140" t="s">
-        <v>4</v>
-      </c>
-      <c r="I140">
-        <v>5.39</v>
+      <c r="A140" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I140" s="5">
+        <v>10</v>
       </c>
       <c r="J140" t="s">
-        <v>5</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="K140" s="1"/>
       <c r="L140" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>1</v>
-      </c>
-      <c r="C141" t="s">
-        <v>9</v>
-      </c>
-      <c r="D141" t="s">
-        <v>3</v>
-      </c>
-      <c r="H141" t="s">
-        <v>4</v>
-      </c>
-      <c r="I141" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J141" t="s">
-        <v>5</v>
-      </c>
+      <c r="A141" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I141" s="5">
+        <v>60</v>
+      </c>
+      <c r="J141" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K141" s="1"/>
       <c r="L141" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>1</v>
-      </c>
-      <c r="C142" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142" t="s">
-        <v>3</v>
-      </c>
-      <c r="E142" t="s">
-        <v>19</v>
-      </c>
-      <c r="H142" t="s">
-        <v>4</v>
-      </c>
-      <c r="I142" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="J142" t="s">
-        <v>5</v>
-      </c>
-      <c r="L142" t="s">
-        <v>10</v>
-      </c>
+      <c r="A142" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I142" s="5">
+        <v>75</v>
+      </c>
+      <c r="J142" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K142" s="1"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>1</v>
-      </c>
-      <c r="D143" t="s">
-        <v>12</v>
-      </c>
-      <c r="H143" t="s">
-        <v>4</v>
-      </c>
-      <c r="I143">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J143" t="s">
-        <v>5</v>
-      </c>
-      <c r="L143" t="s">
-        <v>10</v>
-      </c>
+      <c r="A143" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B143" s="5"/>
+      <c r="C143" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D143" s="5"/>
+      <c r="E143" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I143" s="5">
+        <v>60</v>
+      </c>
+      <c r="J143" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K143" s="1"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>1</v>
-      </c>
-      <c r="D144" t="s">
-        <v>13</v>
-      </c>
-      <c r="H144" t="s">
-        <v>4</v>
-      </c>
-      <c r="I144">
-        <v>0.79</v>
-      </c>
-      <c r="J144" t="s">
-        <v>5</v>
-      </c>
-      <c r="K144" t="s">
-        <v>14</v>
-      </c>
-      <c r="L144" t="s">
-        <v>10</v>
-      </c>
+      <c r="A144" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B144" s="5"/>
+      <c r="C144" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D144" s="5"/>
+      <c r="E144" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I144" s="5">
+        <v>40</v>
+      </c>
+      <c r="J144" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K144" s="1"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="C145" t="s">
+        <v>65</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
-      </c>
-      <c r="H145" t="s">
-        <v>4</v>
+        <v>66</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="I145">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J145" t="s">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="J145" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="L145" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>1</v>
-      </c>
-      <c r="D146" t="s">
-        <v>15</v>
-      </c>
-      <c r="H146" t="s">
-        <v>4</v>
-      </c>
-      <c r="I146">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J146" t="s">
-        <v>5</v>
-      </c>
-      <c r="L146" t="s">
-        <v>10</v>
+      <c r="A146" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I146" s="5">
+        <v>75</v>
+      </c>
+      <c r="J146" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K146" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>1</v>
-      </c>
-      <c r="D147" t="s">
-        <v>17</v>
-      </c>
-      <c r="H147" t="s">
-        <v>4</v>
-      </c>
-      <c r="I147">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J147" t="s">
-        <v>5</v>
+      <c r="A147" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I147" s="5">
+        <v>60</v>
+      </c>
+      <c r="J147" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="K147" t="s">
-        <v>18</v>
-      </c>
-      <c r="L147" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>43</v>
-      </c>
-      <c r="D148" t="s">
-        <v>50</v>
-      </c>
-      <c r="H148" t="s">
-        <v>4</v>
-      </c>
-      <c r="I148">
-        <v>0.69</v>
-      </c>
-      <c r="J148" t="s">
-        <v>5</v>
-      </c>
-      <c r="L148" t="s">
-        <v>10</v>
+      <c r="A148" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D148" s="1"/>
+      <c r="E148" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I148" s="5">
+        <v>40</v>
+      </c>
+      <c r="J148" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K148" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>43</v>
       </c>
-      <c r="D149" t="s">
-        <v>51</v>
+      <c r="E149" t="s">
+        <v>24</v>
       </c>
       <c r="H149" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I149">
-        <v>0.45</v>
+        <v>70</v>
       </c>
       <c r="J149" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="L149" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>43</v>
       </c>
-      <c r="D150" t="s">
-        <v>52</v>
+      <c r="E150" t="s">
+        <v>25</v>
       </c>
       <c r="H150" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I150">
-        <v>4.3999999999999997E-2</v>
+        <v>51</v>
       </c>
       <c r="J150" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="L150" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>43</v>
       </c>
-      <c r="D151" t="s">
-        <v>53</v>
+      <c r="E151" t="s">
+        <v>26</v>
       </c>
       <c r="H151" t="s">
+        <v>33</v>
+      </c>
+      <c r="I151">
+        <v>10</v>
+      </c>
+      <c r="J151" t="s">
+        <v>73</v>
+      </c>
+      <c r="L151" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H153" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I153" s="1">
+        <v>0</v>
+      </c>
+      <c r="J153" s="1"/>
+      <c r="K153" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H154" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I154" s="1">
+        <v>0</v>
+      </c>
+      <c r="J154" s="1"/>
+      <c r="K154" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H155" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I155" s="1">
+        <v>0</v>
+      </c>
+      <c r="J155" s="1"/>
+      <c r="K155" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
+      <c r="K156" s="1"/>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3"/>
+      <c r="L157" s="3"/>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H158" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I151">
-        <v>0.69</v>
-      </c>
-      <c r="J151" t="s">
+      <c r="I158" s="7">
+        <v>0</v>
+      </c>
+      <c r="J158" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="K151" t="s">
-        <v>82</v>
-      </c>
-      <c r="L151" t="s">
+      <c r="K158" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1</v>
+      </c>
+      <c r="C159" t="s">
+        <v>2</v>
+      </c>
+      <c r="D159" t="s">
+        <v>3</v>
+      </c>
+      <c r="H159" t="s">
+        <v>4</v>
+      </c>
+      <c r="I159">
+        <v>5.39</v>
+      </c>
+      <c r="J159" t="s">
+        <v>5</v>
+      </c>
+      <c r="L159" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1</v>
+      </c>
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" t="s">
+        <v>3</v>
+      </c>
+      <c r="H160" t="s">
+        <v>4</v>
+      </c>
+      <c r="I160" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J160" t="s">
+        <v>5</v>
+      </c>
+      <c r="L160" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>43</v>
-      </c>
-      <c r="D152" t="s">
-        <v>44</v>
-      </c>
-      <c r="H152" t="s">
-        <v>4</v>
-      </c>
-      <c r="I152">
-        <v>0.37</v>
-      </c>
-      <c r="J152" t="s">
-        <v>5</v>
-      </c>
-      <c r="L152" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>43</v>
-      </c>
-      <c r="D153" t="s">
-        <v>45</v>
-      </c>
-      <c r="H153" t="s">
-        <v>4</v>
-      </c>
-      <c r="I153">
-        <v>0.37</v>
-      </c>
-      <c r="J153" t="s">
-        <v>5</v>
-      </c>
-      <c r="L153" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H155" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I155" s="7">
-        <v>0</v>
-      </c>
-      <c r="J155" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K155" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>1</v>
-      </c>
-      <c r="C156" t="s">
-        <v>2</v>
-      </c>
-      <c r="D156" t="s">
-        <v>3</v>
-      </c>
-      <c r="H156" t="s">
-        <v>83</v>
-      </c>
-      <c r="I156">
-        <v>0.24</v>
-      </c>
-      <c r="J156" t="s">
-        <v>84</v>
-      </c>
-      <c r="L156" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>1</v>
-      </c>
-      <c r="H157" t="s">
-        <v>83</v>
-      </c>
-      <c r="I157">
-        <v>0.18</v>
-      </c>
-      <c r="J157" t="s">
-        <v>84</v>
-      </c>
-      <c r="L157" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>43</v>
-      </c>
-      <c r="H158" t="s">
-        <v>83</v>
-      </c>
-      <c r="I158">
-        <v>0.45</v>
-      </c>
-      <c r="J158" t="s">
-        <v>84</v>
-      </c>
-      <c r="L158" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H160" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I160" s="7">
-        <v>0</v>
-      </c>
-      <c r="J160" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K160" s="7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="C161" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E161" t="s">
+        <v>19</v>
       </c>
       <c r="H161" t="s">
-        <v>87</v>
-      </c>
-      <c r="I161">
-        <v>1.56</v>
+        <v>4</v>
+      </c>
+      <c r="I161" s="6">
+        <v>3.17</v>
       </c>
       <c r="J161" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="L161" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>88</v>
+        <v>1</v>
+      </c>
+      <c r="D162" t="s">
+        <v>12</v>
       </c>
       <c r="H162" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="I162">
-        <v>0.19</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J162" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="L162" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>64</v>
-      </c>
-      <c r="C163" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
+        <v>13</v>
       </c>
       <c r="H163" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="I163">
-        <v>0.02</v>
+        <v>0.79</v>
       </c>
       <c r="J163" t="s">
-        <v>86</v>
+        <v>5</v>
+      </c>
+      <c r="K163" t="s">
+        <v>14</v>
       </c>
       <c r="L163" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>1</v>
+      </c>
+      <c r="D164" t="s">
+        <v>16</v>
+      </c>
+      <c r="H164" t="s">
+        <v>4</v>
+      </c>
+      <c r="I164">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J164" t="s">
+        <v>5</v>
+      </c>
+      <c r="L164" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>1</v>
+      </c>
+      <c r="D165" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" t="s">
+        <v>4</v>
+      </c>
+      <c r="I165">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J165" t="s">
+        <v>5</v>
+      </c>
+      <c r="L165" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>1</v>
+      </c>
+      <c r="D166" t="s">
+        <v>17</v>
+      </c>
+      <c r="H166" t="s">
+        <v>4</v>
+      </c>
+      <c r="I166">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J166" t="s">
+        <v>5</v>
+      </c>
+      <c r="K166" t="s">
+        <v>18</v>
+      </c>
+      <c r="L166" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>43</v>
+      </c>
+      <c r="D167" t="s">
+        <v>50</v>
+      </c>
+      <c r="H167" t="s">
+        <v>4</v>
+      </c>
+      <c r="I167">
+        <v>0.69</v>
+      </c>
+      <c r="J167" t="s">
+        <v>5</v>
+      </c>
+      <c r="L167" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>43</v>
+      </c>
+      <c r="D168" t="s">
+        <v>51</v>
+      </c>
+      <c r="H168" t="s">
+        <v>4</v>
+      </c>
+      <c r="I168">
+        <v>0.45</v>
+      </c>
+      <c r="J168" t="s">
+        <v>5</v>
+      </c>
+      <c r="L168" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>43</v>
+      </c>
+      <c r="D169" t="s">
+        <v>52</v>
+      </c>
+      <c r="H169" t="s">
+        <v>4</v>
+      </c>
+      <c r="I169">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="J169" t="s">
+        <v>5</v>
+      </c>
+      <c r="L169" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>43</v>
+      </c>
+      <c r="D170" t="s">
+        <v>53</v>
+      </c>
+      <c r="H170" t="s">
+        <v>4</v>
+      </c>
+      <c r="I170">
+        <v>0.69</v>
+      </c>
+      <c r="J170" t="s">
+        <v>5</v>
+      </c>
+      <c r="K170" t="s">
+        <v>77</v>
+      </c>
+      <c r="L170" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>43</v>
+      </c>
+      <c r="D171" t="s">
+        <v>44</v>
+      </c>
+      <c r="H171" t="s">
+        <v>4</v>
+      </c>
+      <c r="I171">
+        <v>0.37</v>
+      </c>
+      <c r="J171" t="s">
+        <v>5</v>
+      </c>
+      <c r="L171" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>43</v>
+      </c>
+      <c r="D172" t="s">
+        <v>45</v>
+      </c>
+      <c r="H172" t="s">
+        <v>4</v>
+      </c>
+      <c r="I172">
+        <v>0.37</v>
+      </c>
+      <c r="J172" t="s">
+        <v>5</v>
+      </c>
+      <c r="L172" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H174" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I174" s="7">
+        <v>0</v>
+      </c>
+      <c r="J174" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K174" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D175" t="s">
+        <v>3</v>
+      </c>
+      <c r="H175" t="s">
+        <v>78</v>
+      </c>
+      <c r="I175">
+        <v>0.24</v>
+      </c>
+      <c r="J175" t="s">
+        <v>79</v>
+      </c>
+      <c r="L175" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>1</v>
+      </c>
+      <c r="H176" t="s">
+        <v>78</v>
+      </c>
+      <c r="I176">
+        <v>0.18</v>
+      </c>
+      <c r="J176" t="s">
+        <v>79</v>
+      </c>
+      <c r="L176" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>43</v>
+      </c>
+      <c r="H177" t="s">
+        <v>78</v>
+      </c>
+      <c r="I177">
+        <v>0.45</v>
+      </c>
+      <c r="J177" t="s">
+        <v>79</v>
+      </c>
+      <c r="L177" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H179" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I179" s="7">
+        <v>0</v>
+      </c>
+      <c r="J179" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K179" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>69</v>
+      </c>
+      <c r="H180" t="s">
+        <v>82</v>
+      </c>
+      <c r="I180">
+        <v>1.56</v>
+      </c>
+      <c r="J180" t="s">
+        <v>81</v>
+      </c>
+      <c r="L180" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>83</v>
+      </c>
+      <c r="H181" t="s">
+        <v>82</v>
+      </c>
+      <c r="I181">
+        <v>0.19</v>
+      </c>
+      <c r="J181" t="s">
+        <v>81</v>
+      </c>
+      <c r="L181" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>64</v>
       </c>
-      <c r="C164" t="s">
-        <v>89</v>
-      </c>
-      <c r="H164" t="s">
+      <c r="C182" t="s">
+        <v>65</v>
+      </c>
+      <c r="H182" t="s">
+        <v>82</v>
+      </c>
+      <c r="I182">
+        <v>0.02</v>
+      </c>
+      <c r="J182" t="s">
+        <v>81</v>
+      </c>
+      <c r="L182" t="s">
         <v>87</v>
       </c>
-      <c r="I164">
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>64</v>
+      </c>
+      <c r="C183" t="s">
+        <v>84</v>
+      </c>
+      <c r="H183" t="s">
+        <v>82</v>
+      </c>
+      <c r="I183">
         <v>0.03</v>
       </c>
-      <c r="J164" t="s">
+      <c r="J183" t="s">
+        <v>81</v>
+      </c>
+      <c r="L183" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E185" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H185" t="s">
+        <v>85</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185" t="s">
         <v>86</v>
       </c>
-      <c r="L164" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E166" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H166" t="s">
-        <v>90</v>
-      </c>
-      <c r="I166">
-        <v>1</v>
-      </c>
-      <c r="J166" t="s">
-        <v>91</v>
-      </c>
-      <c r="L166" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E167" s="5" t="s">
+      <c r="L185" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E186" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H167" t="s">
-        <v>90</v>
-      </c>
-      <c r="I167">
+      <c r="H186" t="s">
+        <v>85</v>
+      </c>
+      <c r="I186">
         <v>3.5</v>
       </c>
-      <c r="J167" t="s">
-        <v>91</v>
-      </c>
-      <c r="L167" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E168" s="5" t="s">
+      <c r="J186" t="s">
+        <v>86</v>
+      </c>
+      <c r="L186" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E187" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H168" t="s">
-        <v>90</v>
-      </c>
-      <c r="I168">
+      <c r="H187" t="s">
+        <v>85</v>
+      </c>
+      <c r="I187">
         <v>2</v>
       </c>
-      <c r="J168" t="s">
-        <v>91</v>
-      </c>
-      <c r="L168" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E169" s="5" t="s">
+      <c r="J187" t="s">
+        <v>86</v>
+      </c>
+      <c r="L187" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E188" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H169" t="s">
-        <v>90</v>
-      </c>
-      <c r="I169">
+      <c r="H188" t="s">
+        <v>85</v>
+      </c>
+      <c r="I188">
         <v>17</v>
       </c>
-      <c r="J169" t="s">
-        <v>91</v>
-      </c>
-      <c r="L169" t="s">
-        <v>92</v>
+      <c r="J188" t="s">
+        <v>86</v>
+      </c>
+      <c r="L188" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="98">
   <si>
     <t>value</t>
   </si>
@@ -295,12 +295,33 @@
   </si>
   <si>
     <t>Swedish IIR 2023 Table 5-7</t>
+  </si>
+  <si>
+    <t>UE_of_GE</t>
+  </si>
+  <si>
+    <t>IPCC 2006 Vol. 4 Eq. 10.24</t>
+  </si>
+  <si>
+    <t>MJ UE/MJ GE</t>
+  </si>
+  <si>
+    <t>Urinary energy expressed as fraction of GE</t>
+  </si>
+  <si>
+    <t>IPCC 2006 Vol.4 Table 10A-9</t>
+  </si>
+  <si>
+    <t>Not used</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -459,7 +480,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,6 +666,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFABAB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -806,15 +833,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="14" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -862,6 +893,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFABAB"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1136,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -4877,547 +4913,907 @@
       <c r="K157" s="3"/>
       <c r="L157" s="3"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H158" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I158" s="7">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H159" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I159" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="J159" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K159" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L159" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I160" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="J160" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="L160" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H162" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I162" s="6">
         <v>0</v>
       </c>
-      <c r="J158" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="K158" s="7" t="s">
+      <c r="J162" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K162" s="6" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>1</v>
-      </c>
-      <c r="C159" t="s">
-        <v>2</v>
-      </c>
-      <c r="D159" t="s">
-        <v>3</v>
-      </c>
-      <c r="H159" t="s">
-        <v>4</v>
-      </c>
-      <c r="I159">
-        <v>5.39</v>
-      </c>
-      <c r="J159" t="s">
-        <v>5</v>
-      </c>
-      <c r="L159" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>1</v>
-      </c>
-      <c r="C160" t="s">
-        <v>9</v>
-      </c>
-      <c r="D160" t="s">
-        <v>3</v>
-      </c>
-      <c r="H160" t="s">
-        <v>4</v>
-      </c>
-      <c r="I160" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J160" t="s">
-        <v>5</v>
-      </c>
-      <c r="L160" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>1</v>
-      </c>
-      <c r="C161" t="s">
-        <v>9</v>
-      </c>
-      <c r="D161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E161" t="s">
-        <v>19</v>
-      </c>
-      <c r="H161" t="s">
-        <v>4</v>
-      </c>
-      <c r="I161" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="J161" t="s">
-        <v>5</v>
-      </c>
-      <c r="L161" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>1</v>
-      </c>
-      <c r="D162" t="s">
-        <v>12</v>
-      </c>
-      <c r="H162" t="s">
-        <v>4</v>
-      </c>
-      <c r="I162">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J162" t="s">
-        <v>5</v>
-      </c>
-      <c r="L162" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1</v>
       </c>
+      <c r="C163" t="s">
+        <v>2</v>
+      </c>
       <c r="D163" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H163" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="I163">
-        <v>0.79</v>
+        <v>0.24</v>
       </c>
       <c r="J163" t="s">
-        <v>5</v>
-      </c>
-      <c r="K163" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="L163" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1</v>
       </c>
-      <c r="D164" t="s">
-        <v>16</v>
-      </c>
       <c r="H164" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="I164">
-        <v>2.2599999999999998</v>
+        <v>0.18</v>
       </c>
       <c r="J164" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="L164" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>1</v>
-      </c>
-      <c r="D165" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="H165" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="I165">
-        <v>2.2599999999999998</v>
+        <v>0.19</v>
       </c>
       <c r="J165" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="L165" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>1</v>
-      </c>
-      <c r="D166" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="H166" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="I166">
-        <v>2.2599999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="J166" t="s">
-        <v>5</v>
-      </c>
-      <c r="K166" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="L166" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>43</v>
       </c>
-      <c r="D167" t="s">
-        <v>50</v>
-      </c>
       <c r="H167" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="I167">
-        <v>0.69</v>
+        <v>0.45</v>
       </c>
       <c r="J167" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="L167" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>43</v>
-      </c>
-      <c r="D168" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="C168" t="s">
+        <v>65</v>
       </c>
       <c r="H168" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="I168">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="J168" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="L168" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>64</v>
+      </c>
+      <c r="C169" t="s">
+        <v>84</v>
+      </c>
+      <c r="H169" t="s">
+        <v>78</v>
+      </c>
+      <c r="I169">
+        <v>0.39</v>
+      </c>
+      <c r="J169" t="s">
+        <v>79</v>
+      </c>
+      <c r="L169" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E171" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H171" t="s">
+        <v>85</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171" t="s">
+        <v>86</v>
+      </c>
+      <c r="L171" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E172" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H172" t="s">
+        <v>85</v>
+      </c>
+      <c r="I172">
+        <v>3.5</v>
+      </c>
+      <c r="J172" t="s">
+        <v>86</v>
+      </c>
+      <c r="L172" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E173" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H173" t="s">
+        <v>85</v>
+      </c>
+      <c r="I173">
+        <v>2</v>
+      </c>
+      <c r="J173" t="s">
+        <v>86</v>
+      </c>
+      <c r="L173" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E174" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H174" t="s">
+        <v>85</v>
+      </c>
+      <c r="I174">
+        <v>17</v>
+      </c>
+      <c r="J174" t="s">
+        <v>86</v>
+      </c>
+      <c r="L174" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B176" s="8"/>
+      <c r="C176" s="8"/>
+      <c r="D176" s="8"/>
+      <c r="E176" s="8"/>
+      <c r="F176" s="8"/>
+      <c r="G176" s="8"/>
+      <c r="H176" s="8"/>
+      <c r="I176" s="8"/>
+      <c r="J176" s="8"/>
+      <c r="K176" s="8"/>
+      <c r="L176" s="8"/>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" s="8"/>
+      <c r="B177" s="8"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="8"/>
+      <c r="E177" s="8"/>
+      <c r="F177" s="8"/>
+      <c r="G177" s="8"/>
+      <c r="H177" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I177" s="9">
+        <v>0</v>
+      </c>
+      <c r="J177" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K177" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L177" s="8"/>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B178" s="9"/>
+      <c r="C178" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E178" s="9"/>
+      <c r="F178" s="9"/>
+      <c r="G178" s="9"/>
+      <c r="H178" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I178" s="9">
+        <v>5.39</v>
+      </c>
+      <c r="J178" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K178" s="9"/>
+      <c r="L178" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E179" s="9"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="9"/>
+      <c r="H179" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I179" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J179" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K179" s="9"/>
+      <c r="L179" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F180" s="9"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I180" s="10">
+        <v>3.17</v>
+      </c>
+      <c r="J180" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K180" s="9"/>
+      <c r="L180" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E181" s="9"/>
+      <c r="F181" s="9"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I181" s="9">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J181" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K181" s="9"/>
+      <c r="L181" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B182" s="9"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" s="9"/>
+      <c r="F182" s="9"/>
+      <c r="G182" s="9"/>
+      <c r="H182" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I182" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="J182" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K182" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L182" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
+      <c r="D183" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183" s="9"/>
+      <c r="F183" s="9"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I183" s="9">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J183" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K183" s="9"/>
+      <c r="L183" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
+      <c r="D184" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E184" s="9"/>
+      <c r="F184" s="9"/>
+      <c r="G184" s="9"/>
+      <c r="H184" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I184" s="9">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J184" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K184" s="9"/>
+      <c r="L184" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185" s="9"/>
+      <c r="F185" s="9"/>
+      <c r="G185" s="9"/>
+      <c r="H185" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I185" s="9">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="J185" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K185" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L185" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
+      <c r="F186" s="9"/>
+      <c r="G186" s="9"/>
+      <c r="H186" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I186" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="J186" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K186" s="9"/>
+      <c r="L186" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
+      <c r="F187" s="9"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I187" s="9">
+        <v>2.13</v>
+      </c>
+      <c r="J187" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K187" s="9"/>
+      <c r="L187" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D169" t="s">
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E188" s="9"/>
+      <c r="F188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I188" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="J188" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K188" s="9"/>
+      <c r="L188" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E189" s="9"/>
+      <c r="F189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I189" s="9">
+        <v>0.45</v>
+      </c>
+      <c r="J189" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K189" s="9"/>
+      <c r="L189" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H169" t="s">
+      <c r="E190" s="9"/>
+      <c r="F190" s="9"/>
+      <c r="G190" s="9"/>
+      <c r="H190" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I169">
+      <c r="I190" s="9">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J169" t="s">
+      <c r="J190" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L169" t="s">
+      <c r="K190" s="9"/>
+      <c r="L190" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D170" t="s">
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H170" t="s">
+      <c r="E191" s="9"/>
+      <c r="F191" s="9"/>
+      <c r="G191" s="9"/>
+      <c r="H191" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I170">
+      <c r="I191" s="9">
         <v>0.69</v>
       </c>
-      <c r="J170" t="s">
+      <c r="J191" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K170" t="s">
+      <c r="K191" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L170" t="s">
+      <c r="L191" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D171" t="s">
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H171" t="s">
+      <c r="E192" s="9"/>
+      <c r="F192" s="9"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I171">
+      <c r="I192" s="9">
         <v>0.37</v>
       </c>
-      <c r="J171" t="s">
+      <c r="J192" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L171" t="s">
+      <c r="K192" s="9"/>
+      <c r="L192" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D172" t="s">
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H172" t="s">
+      <c r="E193" s="9"/>
+      <c r="F193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I172">
+      <c r="I193" s="9">
         <v>0.37</v>
       </c>
-      <c r="J172" t="s">
+      <c r="J193" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="L172" t="s">
+      <c r="K193" s="9"/>
+      <c r="L193" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H174" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I174" s="7">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
+      <c r="D194" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E194" s="9"/>
+      <c r="F194" s="9"/>
+      <c r="G194" s="9"/>
+      <c r="H194" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I194" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="J194" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K194" s="9"/>
+      <c r="L194" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B195" s="9"/>
+      <c r="C195" s="9"/>
+      <c r="D195" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E195" s="9"/>
+      <c r="F195" s="9"/>
+      <c r="G195" s="9"/>
+      <c r="H195" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I195" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="J195" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K195" s="9"/>
+      <c r="L195" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" s="8"/>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="8"/>
+      <c r="E196" s="8"/>
+      <c r="F196" s="8"/>
+      <c r="G196" s="8"/>
+      <c r="H196" s="8"/>
+      <c r="I196" s="8"/>
+      <c r="J196" s="8"/>
+      <c r="K196" s="8"/>
+      <c r="L196" s="8"/>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" s="9"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
+      <c r="F197" s="9"/>
+      <c r="G197" s="9"/>
+      <c r="H197" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I197" s="9">
         <v>0</v>
       </c>
-      <c r="J174" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K174" s="7" t="s">
+      <c r="J197" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K197" s="9" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>1</v>
-      </c>
-      <c r="C175" t="s">
-        <v>2</v>
-      </c>
-      <c r="D175" t="s">
-        <v>3</v>
-      </c>
-      <c r="H175" t="s">
-        <v>78</v>
-      </c>
-      <c r="I175">
-        <v>0.24</v>
-      </c>
-      <c r="J175" t="s">
-        <v>79</v>
-      </c>
-      <c r="L175" t="s">
+      <c r="L197" s="9"/>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B198" s="9"/>
+      <c r="C198" s="9"/>
+      <c r="D198" s="9"/>
+      <c r="E198" s="9"/>
+      <c r="F198" s="9"/>
+      <c r="G198" s="9"/>
+      <c r="H198" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I198" s="9">
+        <v>1.56</v>
+      </c>
+      <c r="J198" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K198" s="9"/>
+      <c r="L198" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>1</v>
-      </c>
-      <c r="H176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I176">
-        <v>0.18</v>
-      </c>
-      <c r="J176" t="s">
-        <v>79</v>
-      </c>
-      <c r="L176" t="s">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B199" s="9"/>
+      <c r="C199" s="9"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
+      <c r="F199" s="9"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I199" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="J199" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K199" s="9"/>
+      <c r="L199" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>43</v>
-      </c>
-      <c r="H177" t="s">
-        <v>78</v>
-      </c>
-      <c r="I177">
-        <v>0.45</v>
-      </c>
-      <c r="J177" t="s">
-        <v>79</v>
-      </c>
-      <c r="L177" t="s">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
+      <c r="F200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I200" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="J200" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K200" s="9"/>
+      <c r="L200" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H179" s="7" t="s">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
+      <c r="F201" s="9"/>
+      <c r="G201" s="9"/>
+      <c r="H201" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I179" s="7">
-        <v>0</v>
-      </c>
-      <c r="J179" s="7" t="s">
+      <c r="I201" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="J201" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K179" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>69</v>
-      </c>
-      <c r="H180" t="s">
-        <v>82</v>
-      </c>
-      <c r="I180">
-        <v>1.56</v>
-      </c>
-      <c r="J180" t="s">
-        <v>81</v>
-      </c>
-      <c r="L180" t="s">
+      <c r="K201" s="9"/>
+      <c r="L201" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>83</v>
-      </c>
-      <c r="H181" t="s">
-        <v>82</v>
-      </c>
-      <c r="I181">
-        <v>0.19</v>
-      </c>
-      <c r="J181" t="s">
-        <v>81</v>
-      </c>
-      <c r="L181" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>64</v>
-      </c>
-      <c r="C182" t="s">
-        <v>65</v>
-      </c>
-      <c r="H182" t="s">
-        <v>82</v>
-      </c>
-      <c r="I182">
-        <v>0.02</v>
-      </c>
-      <c r="J182" t="s">
-        <v>81</v>
-      </c>
-      <c r="L182" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>64</v>
-      </c>
-      <c r="C183" t="s">
-        <v>84</v>
-      </c>
-      <c r="H183" t="s">
-        <v>82</v>
-      </c>
-      <c r="I183">
-        <v>0.03</v>
-      </c>
-      <c r="J183" t="s">
-        <v>81</v>
-      </c>
-      <c r="L183" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E185" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H185" t="s">
-        <v>85</v>
-      </c>
-      <c r="I185">
-        <v>1</v>
-      </c>
-      <c r="J185" t="s">
-        <v>86</v>
-      </c>
-      <c r="L185" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E186" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H186" t="s">
-        <v>85</v>
-      </c>
-      <c r="I186">
-        <v>3.5</v>
-      </c>
-      <c r="J186" t="s">
-        <v>86</v>
-      </c>
-      <c r="L186" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E187" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H187" t="s">
-        <v>85</v>
-      </c>
-      <c r="I187">
-        <v>2</v>
-      </c>
-      <c r="J187" t="s">
-        <v>86</v>
-      </c>
-      <c r="L187" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E188" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H188" t="s">
-        <v>85</v>
-      </c>
-      <c r="I188">
-        <v>17</v>
-      </c>
-      <c r="J188" t="s">
-        <v>86</v>
-      </c>
-      <c r="L188" t="s">
-        <v>87</v>
-      </c>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I204" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/prod_parameters/ManureMgmt.xlsx
+++ b/data/prod_parameters/ManureMgmt.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="103">
   <si>
     <t>value</t>
   </si>
@@ -313,6 +313,21 @@
   </si>
   <si>
     <t>Not used</t>
+  </si>
+  <si>
+    <t>manure_VS_C</t>
+  </si>
+  <si>
+    <t>Rundgren 2021</t>
+  </si>
+  <si>
+    <t>C_loss</t>
+  </si>
+  <si>
+    <t>Fraction of carbon in excreted manure volatile solids</t>
+  </si>
+  <si>
+    <t>Fraction of carbon in excreted manure lost before application to soil</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M204"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -5161,191 +5176,105 @@
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" s="11" t="s">
+      <c r="H176" t="s">
+        <v>98</v>
+      </c>
+      <c r="I176">
+        <v>55</v>
+      </c>
+      <c r="J176" t="s">
+        <v>21</v>
+      </c>
+      <c r="K176" t="s">
+        <v>101</v>
+      </c>
+      <c r="L176" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E177" s="5"/>
+      <c r="H177" t="s">
+        <v>100</v>
+      </c>
+      <c r="I177">
+        <v>10</v>
+      </c>
+      <c r="J177" t="s">
+        <v>21</v>
+      </c>
+      <c r="K177" t="s">
+        <v>102</v>
+      </c>
+      <c r="L177" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E178" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H178" t="s">
+        <v>100</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E179" s="5"/>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
-      <c r="F176" s="8"/>
-      <c r="G176" s="8"/>
-      <c r="H176" s="8"/>
-      <c r="I176" s="8"/>
-      <c r="J176" s="8"/>
-      <c r="K176" s="8"/>
-      <c r="L176" s="8"/>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="8"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="8"/>
-      <c r="H177" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I177" s="9">
-        <v>0</v>
-      </c>
-      <c r="J177" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K177" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L177" s="8"/>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D178" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I178" s="9">
-        <v>5.39</v>
-      </c>
-      <c r="J178" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K178" s="9"/>
-      <c r="L178" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D179" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I179" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="J179" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K179" s="9"/>
-      <c r="L179" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D180" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F180" s="9"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I180" s="10">
-        <v>3.17</v>
-      </c>
-      <c r="J180" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K180" s="9"/>
-      <c r="L180" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-      <c r="D181" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E181" s="9"/>
-      <c r="F181" s="9"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I181" s="9">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J181" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K181" s="9"/>
-      <c r="L181" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="B181" s="8"/>
+      <c r="C181" s="8"/>
+      <c r="D181" s="8"/>
+      <c r="E181" s="8"/>
+      <c r="F181" s="8"/>
+      <c r="G181" s="8"/>
+      <c r="H181" s="8"/>
+      <c r="I181" s="8"/>
+      <c r="J181" s="8"/>
+      <c r="K181" s="8"/>
+      <c r="L181" s="8"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E182" s="9"/>
-      <c r="F182" s="9"/>
-      <c r="G182" s="9"/>
+      <c r="A182" s="8"/>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8"/>
+      <c r="D182" s="8"/>
+      <c r="E182" s="8"/>
+      <c r="F182" s="8"/>
+      <c r="G182" s="8"/>
       <c r="H182" s="9" t="s">
         <v>4</v>
       </c>
       <c r="I182" s="9">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="J182" s="9" t="s">
         <v>5</v>
       </c>
       <c r="K182" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L182" s="9" t="s">
-        <v>10</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="L182" s="8"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
+      <c r="C183" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D183" s="9" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
@@ -5354,14 +5283,14 @@
         <v>4</v>
       </c>
       <c r="I183" s="9">
-        <v>2.2599999999999998</v>
+        <v>5.39</v>
       </c>
       <c r="J183" s="9" t="s">
         <v>5</v>
       </c>
       <c r="K183" s="9"/>
       <c r="L183" s="9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -5369,9 +5298,11 @@
         <v>1</v>
       </c>
       <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
+      <c r="C184" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="D184" s="9" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E184" s="9"/>
       <c r="F184" s="9"/>
@@ -5379,8 +5310,8 @@
       <c r="H184" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I184" s="9">
-        <v>2.2599999999999998</v>
+      <c r="I184" s="10">
+        <v>2.2999999999999998</v>
       </c>
       <c r="J184" s="9" t="s">
         <v>5</v>
@@ -5395,36 +5326,40 @@
         <v>1</v>
       </c>
       <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
+      <c r="C185" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="D185" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E185" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="F185" s="9"/>
       <c r="G185" s="9"/>
       <c r="H185" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I185" s="9">
-        <v>2.2599999999999998</v>
+      <c r="I185" s="10">
+        <v>3.17</v>
       </c>
       <c r="J185" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K185" s="9" t="s">
-        <v>18</v>
-      </c>
+      <c r="K185" s="9"/>
       <c r="L185" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="9" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
+      <c r="D186" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="E186" s="9"/>
       <c r="F186" s="9"/>
       <c r="G186" s="9"/>
@@ -5432,23 +5367,25 @@
         <v>4</v>
       </c>
       <c r="I186" s="9">
-        <v>0.4</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J186" s="9" t="s">
         <v>5</v>
       </c>
       <c r="K186" s="9"/>
       <c r="L186" s="9" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="9" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
+      <c r="D187" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
       <c r="G187" s="9"/>
@@ -5456,24 +5393,26 @@
         <v>4</v>
       </c>
       <c r="I187" s="9">
-        <v>2.13</v>
+        <v>0.79</v>
       </c>
       <c r="J187" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K187" s="9"/>
+      <c r="K187" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="L187" s="9" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="9" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E188" s="9"/>
       <c r="F188" s="9"/>
@@ -5482,7 +5421,7 @@
         <v>4</v>
       </c>
       <c r="I188" s="9">
-        <v>0.69</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J188" s="9" t="s">
         <v>5</v>
@@ -5494,12 +5433,12 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="9" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="9" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E189" s="9"/>
       <c r="F189" s="9"/>
@@ -5508,7 +5447,7 @@
         <v>4</v>
       </c>
       <c r="I189" s="9">
-        <v>0.45</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J189" s="9" t="s">
         <v>5</v>
@@ -5520,12 +5459,12 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E190" s="9"/>
       <c r="F190" s="9"/>
@@ -5534,25 +5473,25 @@
         <v>4</v>
       </c>
       <c r="I190" s="9">
-        <v>4.3999999999999997E-2</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="J190" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K190" s="9"/>
+      <c r="K190" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="L190" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="9" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
-      <c r="D191" s="9" t="s">
-        <v>53</v>
-      </c>
+      <c r="D191" s="9"/>
       <c r="E191" s="9"/>
       <c r="F191" s="9"/>
       <c r="G191" s="9"/>
@@ -5560,27 +5499,23 @@
         <v>4</v>
       </c>
       <c r="I191" s="9">
-        <v>0.69</v>
+        <v>0.4</v>
       </c>
       <c r="J191" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K191" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="K191" s="9"/>
       <c r="L191" s="9" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
-      <c r="D192" s="9" t="s">
-        <v>44</v>
-      </c>
+      <c r="D192" s="9"/>
       <c r="E192" s="9"/>
       <c r="F192" s="9"/>
       <c r="G192" s="9"/>
@@ -5588,14 +5523,14 @@
         <v>4</v>
       </c>
       <c r="I192" s="9">
-        <v>0.37</v>
+        <v>2.13</v>
       </c>
       <c r="J192" s="9" t="s">
         <v>5</v>
       </c>
       <c r="K192" s="9"/>
       <c r="L192" s="9" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -5605,7 +5540,7 @@
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E193" s="9"/>
       <c r="F193" s="9"/>
@@ -5614,7 +5549,7 @@
         <v>4</v>
       </c>
       <c r="I193" s="9">
-        <v>0.37</v>
+        <v>0.69</v>
       </c>
       <c r="J193" s="9" t="s">
         <v>5</v>
@@ -5626,12 +5561,12 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E194" s="9"/>
       <c r="F194" s="9"/>
@@ -5640,24 +5575,24 @@
         <v>4</v>
       </c>
       <c r="I194" s="9">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
       <c r="J194" s="9" t="s">
         <v>5</v>
       </c>
       <c r="K194" s="9"/>
       <c r="L194" s="9" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="E195" s="9"/>
       <c r="F195" s="9"/>
@@ -5666,98 +5601,120 @@
         <v>4</v>
       </c>
       <c r="I195" s="9">
-        <v>0.02</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="J195" s="9" t="s">
         <v>5</v>
       </c>
       <c r="K195" s="9"/>
       <c r="L195" s="9" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="8"/>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
-      <c r="F196" s="8"/>
-      <c r="G196" s="8"/>
-      <c r="H196" s="8"/>
-      <c r="I196" s="8"/>
-      <c r="J196" s="8"/>
-      <c r="K196" s="8"/>
-      <c r="L196" s="8"/>
+      <c r="A196" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I196" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="J196" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K196" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L196" s="9" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="9"/>
+      <c r="A197" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
-      <c r="D197" s="9"/>
+      <c r="D197" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="E197" s="9"/>
       <c r="F197" s="9"/>
       <c r="G197" s="9"/>
       <c r="H197" s="9" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="I197" s="9">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K197" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L197" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="K197" s="9"/>
+      <c r="L197" s="9" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
-      <c r="D198" s="9"/>
+      <c r="D198" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="E198" s="9"/>
       <c r="F198" s="9"/>
       <c r="G198" s="9"/>
       <c r="H198" s="9" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="I198" s="9">
-        <v>1.56</v>
+        <v>0.37</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="K198" s="9"/>
       <c r="L198" s="9" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
+      <c r="D199" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="E199" s="9"/>
       <c r="F199" s="9"/>
       <c r="G199" s="9"/>
       <c r="H199" s="9" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="I199" s="9">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="J199" s="9" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="K199" s="9"/>
       <c r="L199" s="9" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -5765,55 +5722,165 @@
         <v>64</v>
       </c>
       <c r="B200" s="9"/>
-      <c r="C200" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D200" s="9"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="E200" s="9"/>
       <c r="F200" s="9"/>
       <c r="G200" s="9"/>
       <c r="H200" s="9" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="I200" s="9">
         <v>0.02</v>
       </c>
       <c r="J200" s="9" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="K200" s="9"/>
       <c r="L200" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" s="8"/>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="8"/>
+      <c r="E201" s="8"/>
+      <c r="F201" s="8"/>
+      <c r="G201" s="8"/>
+      <c r="H201" s="8"/>
+      <c r="I201" s="8"/>
+      <c r="J201" s="8"/>
+      <c r="K201" s="8"/>
+      <c r="L201" s="8"/>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" s="9"/>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
+      <c r="F202" s="9"/>
+      <c r="G202" s="9"/>
+      <c r="H202" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I202" s="9">
+        <v>0</v>
+      </c>
+      <c r="J202" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K202" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L202" s="9"/>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9"/>
+      <c r="G203" s="9"/>
+      <c r="H203" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I203" s="9">
+        <v>1.56</v>
+      </c>
+      <c r="J203" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K203" s="9"/>
+      <c r="L203" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="9" t="s">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
+      <c r="F204" s="9"/>
+      <c r="G204" s="9"/>
+      <c r="H204" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I204" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="J204" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K204" s="9"/>
+      <c r="L204" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9" t="s">
+      <c r="B205" s="9"/>
+      <c r="C205" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9"/>
+      <c r="H205" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I205" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="J205" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K205" s="9"/>
+      <c r="L205" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A206" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B206" s="9"/>
+      <c r="C206" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D201" s="9"/>
-      <c r="E201" s="9"/>
-      <c r="F201" s="9"/>
-      <c r="G201" s="9"/>
-      <c r="H201" s="9" t="s">
+      <c r="D206" s="9"/>
+      <c r="E206" s="9"/>
+      <c r="F206" s="9"/>
+      <c r="G206" s="9"/>
+      <c r="H206" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I201" s="9">
+      <c r="I206" s="9">
         <v>0.03</v>
       </c>
-      <c r="J201" s="9" t="s">
+      <c r="J206" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K201" s="9"/>
-      <c r="L201" s="9" t="s">
+      <c r="K206" s="9"/>
+      <c r="L206" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I204" s="7"/>
+    <row r="209" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I209" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
